--- a/docs/项目填报模板.xlsx
+++ b/docs/项目填报模板.xlsx
@@ -535,35 +535,35 @@
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>4. 市场列已区分国内/海外，所有项目填在同一个 Sheet 即可。</t>
+          <t>4. 市场列按销售区域选择（拉美区/西欧区/东欧区/中东区/亚太区/土耳其区/非洲区/北美区/OEM业务部）。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>5. 项目编号仅用于行归类（项目行/阶段行）、阶段归属与排序，导入后系统自动重新编号。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>阶段依赖关系</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>导入后，系统会自动按阶段序号生成 FS（完成-开始）依赖链：</t>
-        </is>
-      </c>
+      <c r="C11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　例如项目 1 有阶段 1-1→1-2→1-3→1-4，导入后自动串联依赖。</t>
+          <t>导入后，系统会自动按阶段序号生成 FS（完成-开始）依赖链：</t>
         </is>
       </c>
     </row>
@@ -571,139 +571,135 @@
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>如需更复杂的依赖类型（SS 并行 / 跨阶段），请在系统甘特图中手动调整。</t>
+          <t xml:space="preserve">　例如项目 1 有阶段 1-1→1-2→1-3→1-4，导入后自动串联依赖。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>如需更复杂的依赖类型（SS 并行 / 跨阶段），请在系统甘特图中手动调整。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>字段说明</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>项目编号</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>必填。项目行纯数字，阶段行数字-数字（如 1-1）。</t>
-        </is>
-      </c>
+      <c r="C16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>项目类目</t>
+          <t>项目编号</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>必填。下拉选择：新需求 / 量产 / 定制 / 改造。</t>
+          <t>项目行纯数字，阶段行数字-数字（如 1-1）。仅用于行归类/阶段归属/排序，导入后系统自动重新编号。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>项目名称</t>
+          <t>项目类目</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>必填。项目的完整名称。</t>
+          <t>必填。下拉选择：新需求 / 量产 / 定制 / 改造。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>项目负责人</t>
+          <t>项目名称</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>必填。负责该项目的项目经理姓名。</t>
+          <t>必填。项目的完整名称。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>市场</t>
+          <t>项目负责人</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>必填。下拉选择：国内 / 海外。</t>
+          <t>必填。负责该项目的项目经理姓名。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>计划开始/结束</t>
+          <t>市场</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>日期格式 YYYY-MM-DD（如 2026-07-01）。</t>
+          <t>必填。下拉选择销售区域（拉美区/西欧区/东欧区/中东区/亚太区/土耳其区/非洲区/北美区/OEM业务部）。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>实际开始/结束</t>
+          <t>阶段类型</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>日期格式 YYYY-MM-DD。项目行不填，阶段行按实际情况。</t>
+          <t>阶段行必填。下拉选择：需求评估 / 配置评估 / 模块选型 / 工业设计 / 结构设计 / 样机打样 / 联调测试 / 交付。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>阶段类型</t>
+          <t>计划开始/结束</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>阶段行必填。下拉选择：P1 需求评估 ~ P8 交付。</t>
+          <t>日期格式 YYYY-MM-DD（如 2026-07-01）。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>阶段负责人</t>
+          <t>实际开始/结束</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>多人用空格或顿号分隔（如「张三 李四」）。</t>
+          <t>日期格式 YYYY-MM-DD。项目行不填，阶段行按实际情况。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>交接人</t>
+          <t>阶段负责人</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>阶段行可选。该阶段的交接对象。</t>
+          <t>多人用空格或顿号分隔（如「张三 李四」）。</t>
         </is>
       </c>
     </row>
@@ -790,24 +786,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O202"/>
+  <dimension ref="A1:N202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -845,29 +840,29 @@
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
+          <t>阶段类型</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
           <t>计划开始</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>计划结束</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>实际开始</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>实际结束</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>阶段类型</t>
-        </is>
-      </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
           <t>阶段负责人</t>
@@ -875,20 +870,15 @@
       </c>
       <c r="L2" s="6" t="inlineStr">
         <is>
-          <t>交接人</t>
+          <t>阶段状态</t>
         </is>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
-          <t>阶段状态</t>
+          <t>阶段进度</t>
         </is>
       </c>
       <c r="N2" s="6" t="inlineStr">
-        <is>
-          <t>阶段进度</t>
-        </is>
-      </c>
-      <c r="O2" s="6" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -898,7 +888,7 @@
       <c r="A3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>新需求</t>
         </is>
@@ -915,27 +905,30 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
+          <t>拉美区</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr"/>
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr"/>
       <c r="I3" s="7" t="inlineStr"/>
       <c r="J3" s="7" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
       <c r="L3" s="7" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
-      <c r="N3" s="7" t="inlineStr"/>
-      <c r="O3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr">
+        <is>
+          <t>可描述项目内容、背景、风险等</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -943,50 +936,49 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr"/>
       <c r="C4" s="8" t="inlineStr"/>
       <c r="D4" s="7" t="inlineStr"/>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr">
         <is>
+          <t>工业设计</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>P4 工业设计</t>
-        </is>
-      </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr"/>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="N4" s="7" t="n">
+      <c r="M4" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="O4" s="8" t="inlineStr"/>
+      <c r="N4" s="8" t="inlineStr"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -994,31 +986,31 @@
           <t>1-2</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr"/>
       <c r="C5" s="8" t="inlineStr"/>
       <c r="D5" s="7" t="inlineStr"/>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr">
         <is>
+          <t>结构设计</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr"/>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>P5 结构设计</t>
-        </is>
-      </c>
+      <c r="J5" s="7" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr">
         <is>
           <t>李四 王五</t>
@@ -1026,18 +1018,13 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="N5" s="7" t="n">
+      <c r="M5" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="O5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -1045,42 +1032,41 @@
           <t>1-3</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr"/>
+      <c r="B6" s="7" t="inlineStr"/>
       <c r="C6" s="8" t="inlineStr"/>
       <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="7" t="inlineStr"/>
       <c r="F6" s="7" t="inlineStr">
         <is>
+          <t>联调测试</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr"/>
       <c r="I6" s="7" t="inlineStr"/>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>P7 联调测试</t>
-        </is>
-      </c>
+      <c r="J6" s="7" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr">
         <is>
           <t>王五</t>
         </is>
       </c>
-      <c r="L6" s="7" t="inlineStr"/>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="N6" s="7" t="n">
+      <c r="M6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="N6" s="8" t="inlineStr">
         <is>
           <t>待启动</t>
         </is>
@@ -1088,7 +1074,7 @@
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="7" t="inlineStr"/>
-      <c r="B7" s="8" t="inlineStr"/>
+      <c r="B7" s="7" t="inlineStr"/>
       <c r="C7" s="8" t="inlineStr"/>
       <c r="D7" s="7" t="inlineStr"/>
       <c r="E7" s="7" t="inlineStr"/>
@@ -1100,14 +1086,13 @@
       <c r="K7" s="8" t="inlineStr"/>
       <c r="L7" s="7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
-      <c r="O7" s="8" t="inlineStr"/>
+      <c r="N7" s="8" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>量产</t>
         </is>
@@ -1124,27 +1109,26 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>海外</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
+          <t>中东区</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr"/>
       <c r="I8" s="7" t="inlineStr"/>
       <c r="J8" s="7" t="inlineStr"/>
       <c r="K8" s="8" t="inlineStr"/>
       <c r="L8" s="7" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
-      <c r="O8" s="8" t="inlineStr"/>
+      <c r="N8" s="8" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -1152,46 +1136,45 @@
           <t>2-1</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr"/>
+      <c r="B9" s="7" t="inlineStr"/>
       <c r="C9" s="8" t="inlineStr"/>
       <c r="D9" s="7" t="inlineStr"/>
       <c r="E9" s="7" t="inlineStr"/>
       <c r="F9" s="7" t="inlineStr">
         <is>
+          <t>结构设计</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr"/>
       <c r="I9" s="7" t="inlineStr"/>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>P5 结构设计</t>
-        </is>
-      </c>
+      <c r="J9" s="7" t="inlineStr"/>
       <c r="K9" s="8" t="inlineStr">
         <is>
           <t>钱七</t>
         </is>
       </c>
-      <c r="L9" s="7" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr">
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="N9" s="7" t="n">
+      <c r="M9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="8" t="inlineStr"/>
+      <c r="N9" s="8" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="7" t="n"/>
-      <c r="B10" s="8" t="n"/>
+      <c r="B10" s="7" t="n"/>
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
@@ -1203,12 +1186,11 @@
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="7" t="n"/>
       <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="n"/>
-      <c r="O10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="7" t="n"/>
-      <c r="B11" s="8" t="n"/>
+      <c r="B11" s="7" t="n"/>
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
@@ -1220,12 +1202,11 @@
       <c r="K11" s="8" t="n"/>
       <c r="L11" s="7" t="n"/>
       <c r="M11" s="7" t="n"/>
-      <c r="N11" s="7" t="n"/>
-      <c r="O11" s="8" t="n"/>
+      <c r="N11" s="8" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="7" t="n"/>
-      <c r="B12" s="8" t="n"/>
+      <c r="B12" s="7" t="n"/>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
@@ -1237,12 +1218,11 @@
       <c r="K12" s="8" t="n"/>
       <c r="L12" s="7" t="n"/>
       <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="n"/>
-      <c r="O12" s="8" t="n"/>
+      <c r="N12" s="8" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="7" t="n"/>
-      <c r="B13" s="8" t="n"/>
+      <c r="B13" s="7" t="n"/>
       <c r="C13" s="8" t="n"/>
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
@@ -1254,12 +1234,11 @@
       <c r="K13" s="8" t="n"/>
       <c r="L13" s="7" t="n"/>
       <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
-      <c r="O13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="7" t="n"/>
-      <c r="B14" s="8" t="n"/>
+      <c r="B14" s="7" t="n"/>
       <c r="C14" s="8" t="n"/>
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
@@ -1271,12 +1250,11 @@
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="7" t="n"/>
       <c r="M14" s="7" t="n"/>
-      <c r="N14" s="7" t="n"/>
-      <c r="O14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="7" t="n"/>
-      <c r="B15" s="8" t="n"/>
+      <c r="B15" s="7" t="n"/>
       <c r="C15" s="8" t="n"/>
       <c r="D15" s="7" t="n"/>
       <c r="E15" s="7" t="n"/>
@@ -1288,12 +1266,11 @@
       <c r="K15" s="8" t="n"/>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
-      <c r="N15" s="7" t="n"/>
-      <c r="O15" s="8" t="n"/>
+      <c r="N15" s="8" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="7" t="n"/>
-      <c r="B16" s="8" t="n"/>
+      <c r="B16" s="7" t="n"/>
       <c r="C16" s="8" t="n"/>
       <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
@@ -1305,12 +1282,11 @@
       <c r="K16" s="8" t="n"/>
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>
-      <c r="N16" s="7" t="n"/>
-      <c r="O16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="7" t="n"/>
-      <c r="B17" s="8" t="n"/>
+      <c r="B17" s="7" t="n"/>
       <c r="C17" s="8" t="n"/>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
@@ -1322,12 +1298,11 @@
       <c r="K17" s="8" t="n"/>
       <c r="L17" s="7" t="n"/>
       <c r="M17" s="7" t="n"/>
-      <c r="N17" s="7" t="n"/>
-      <c r="O17" s="8" t="n"/>
+      <c r="N17" s="8" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="7" t="n"/>
-      <c r="B18" s="8" t="n"/>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
@@ -1339,12 +1314,11 @@
       <c r="K18" s="8" t="n"/>
       <c r="L18" s="7" t="n"/>
       <c r="M18" s="7" t="n"/>
-      <c r="N18" s="7" t="n"/>
-      <c r="O18" s="8" t="n"/>
+      <c r="N18" s="8" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="7" t="n"/>
-      <c r="B19" s="8" t="n"/>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
@@ -1356,12 +1330,11 @@
       <c r="K19" s="8" t="n"/>
       <c r="L19" s="7" t="n"/>
       <c r="M19" s="7" t="n"/>
-      <c r="N19" s="7" t="n"/>
-      <c r="O19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="7" t="n"/>
-      <c r="B20" s="8" t="n"/>
+      <c r="B20" s="7" t="n"/>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
@@ -1373,12 +1346,11 @@
       <c r="K20" s="8" t="n"/>
       <c r="L20" s="7" t="n"/>
       <c r="M20" s="7" t="n"/>
-      <c r="N20" s="7" t="n"/>
-      <c r="O20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="7" t="n"/>
-      <c r="B21" s="8" t="n"/>
+      <c r="B21" s="7" t="n"/>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
@@ -1390,12 +1362,11 @@
       <c r="K21" s="8" t="n"/>
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
-      <c r="N21" s="7" t="n"/>
-      <c r="O21" s="8" t="n"/>
+      <c r="N21" s="8" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="7" t="n"/>
-      <c r="B22" s="8" t="n"/>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
@@ -1407,12 +1378,11 @@
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="7" t="n"/>
       <c r="M22" s="7" t="n"/>
-      <c r="N22" s="7" t="n"/>
-      <c r="O22" s="8" t="n"/>
+      <c r="N22" s="8" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="7" t="n"/>
-      <c r="B23" s="8" t="n"/>
+      <c r="B23" s="7" t="n"/>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
@@ -1424,12 +1394,11 @@
       <c r="K23" s="8" t="n"/>
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
-      <c r="N23" s="7" t="n"/>
-      <c r="O23" s="8" t="n"/>
+      <c r="N23" s="8" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="7" t="n"/>
-      <c r="B24" s="8" t="n"/>
+      <c r="B24" s="7" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
@@ -1441,12 +1410,11 @@
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="7" t="n"/>
       <c r="M24" s="7" t="n"/>
-      <c r="N24" s="7" t="n"/>
-      <c r="O24" s="8" t="n"/>
+      <c r="N24" s="8" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="7" t="n"/>
-      <c r="B25" s="8" t="n"/>
+      <c r="B25" s="7" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
@@ -1458,12 +1426,11 @@
       <c r="K25" s="8" t="n"/>
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
-      <c r="N25" s="7" t="n"/>
-      <c r="O25" s="8" t="n"/>
+      <c r="N25" s="8" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="7" t="n"/>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="7" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
@@ -1475,12 +1442,11 @@
       <c r="K26" s="8" t="n"/>
       <c r="L26" s="7" t="n"/>
       <c r="M26" s="7" t="n"/>
-      <c r="N26" s="7" t="n"/>
-      <c r="O26" s="8" t="n"/>
+      <c r="N26" s="8" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="7" t="n"/>
-      <c r="B27" s="8" t="n"/>
+      <c r="B27" s="7" t="n"/>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
@@ -1492,12 +1458,11 @@
       <c r="K27" s="8" t="n"/>
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
-      <c r="N27" s="7" t="n"/>
-      <c r="O27" s="8" t="n"/>
+      <c r="N27" s="8" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="7" t="n"/>
-      <c r="B28" s="8" t="n"/>
+      <c r="B28" s="7" t="n"/>
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
@@ -1509,12 +1474,11 @@
       <c r="K28" s="8" t="n"/>
       <c r="L28" s="7" t="n"/>
       <c r="M28" s="7" t="n"/>
-      <c r="N28" s="7" t="n"/>
-      <c r="O28" s="8" t="n"/>
+      <c r="N28" s="8" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="7" t="n"/>
-      <c r="B29" s="8" t="n"/>
+      <c r="B29" s="7" t="n"/>
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
@@ -1526,12 +1490,11 @@
       <c r="K29" s="8" t="n"/>
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
-      <c r="N29" s="7" t="n"/>
-      <c r="O29" s="8" t="n"/>
+      <c r="N29" s="8" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="7" t="n"/>
-      <c r="B30" s="8" t="n"/>
+      <c r="B30" s="7" t="n"/>
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="7" t="n"/>
       <c r="E30" s="7" t="n"/>
@@ -1543,12 +1506,11 @@
       <c r="K30" s="8" t="n"/>
       <c r="L30" s="7" t="n"/>
       <c r="M30" s="7" t="n"/>
-      <c r="N30" s="7" t="n"/>
-      <c r="O30" s="8" t="n"/>
+      <c r="N30" s="8" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="7" t="n"/>
-      <c r="B31" s="8" t="n"/>
+      <c r="B31" s="7" t="n"/>
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
@@ -1560,12 +1522,11 @@
       <c r="K31" s="8" t="n"/>
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
-      <c r="N31" s="7" t="n"/>
-      <c r="O31" s="8" t="n"/>
+      <c r="N31" s="8" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="7" t="n"/>
-      <c r="B32" s="8" t="n"/>
+      <c r="B32" s="7" t="n"/>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
@@ -1577,12 +1538,11 @@
       <c r="K32" s="8" t="n"/>
       <c r="L32" s="7" t="n"/>
       <c r="M32" s="7" t="n"/>
-      <c r="N32" s="7" t="n"/>
-      <c r="O32" s="8" t="n"/>
+      <c r="N32" s="8" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="7" t="n"/>
-      <c r="B33" s="8" t="n"/>
+      <c r="B33" s="7" t="n"/>
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
@@ -1594,12 +1554,11 @@
       <c r="K33" s="8" t="n"/>
       <c r="L33" s="7" t="n"/>
       <c r="M33" s="7" t="n"/>
-      <c r="N33" s="7" t="n"/>
-      <c r="O33" s="8" t="n"/>
+      <c r="N33" s="8" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="7" t="n"/>
-      <c r="B34" s="8" t="n"/>
+      <c r="B34" s="7" t="n"/>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
@@ -1611,12 +1570,11 @@
       <c r="K34" s="8" t="n"/>
       <c r="L34" s="7" t="n"/>
       <c r="M34" s="7" t="n"/>
-      <c r="N34" s="7" t="n"/>
-      <c r="O34" s="8" t="n"/>
+      <c r="N34" s="8" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="7" t="n"/>
-      <c r="B35" s="8" t="n"/>
+      <c r="B35" s="7" t="n"/>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
@@ -1628,12 +1586,11 @@
       <c r="K35" s="8" t="n"/>
       <c r="L35" s="7" t="n"/>
       <c r="M35" s="7" t="n"/>
-      <c r="N35" s="7" t="n"/>
-      <c r="O35" s="8" t="n"/>
+      <c r="N35" s="8" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="7" t="n"/>
-      <c r="B36" s="8" t="n"/>
+      <c r="B36" s="7" t="n"/>
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
@@ -1645,12 +1602,11 @@
       <c r="K36" s="8" t="n"/>
       <c r="L36" s="7" t="n"/>
       <c r="M36" s="7" t="n"/>
-      <c r="N36" s="7" t="n"/>
-      <c r="O36" s="8" t="n"/>
+      <c r="N36" s="8" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="7" t="n"/>
-      <c r="B37" s="8" t="n"/>
+      <c r="B37" s="7" t="n"/>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
@@ -1662,12 +1618,11 @@
       <c r="K37" s="8" t="n"/>
       <c r="L37" s="7" t="n"/>
       <c r="M37" s="7" t="n"/>
-      <c r="N37" s="7" t="n"/>
-      <c r="O37" s="8" t="n"/>
+      <c r="N37" s="8" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="7" t="n"/>
-      <c r="B38" s="8" t="n"/>
+      <c r="B38" s="7" t="n"/>
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
@@ -1679,12 +1634,11 @@
       <c r="K38" s="8" t="n"/>
       <c r="L38" s="7" t="n"/>
       <c r="M38" s="7" t="n"/>
-      <c r="N38" s="7" t="n"/>
-      <c r="O38" s="8" t="n"/>
+      <c r="N38" s="8" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="7" t="n"/>
-      <c r="B39" s="8" t="n"/>
+      <c r="B39" s="7" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
@@ -1696,12 +1650,11 @@
       <c r="K39" s="8" t="n"/>
       <c r="L39" s="7" t="n"/>
       <c r="M39" s="7" t="n"/>
-      <c r="N39" s="7" t="n"/>
-      <c r="O39" s="8" t="n"/>
+      <c r="N39" s="8" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="7" t="n"/>
-      <c r="B40" s="8" t="n"/>
+      <c r="B40" s="7" t="n"/>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
@@ -1713,12 +1666,11 @@
       <c r="K40" s="8" t="n"/>
       <c r="L40" s="7" t="n"/>
       <c r="M40" s="7" t="n"/>
-      <c r="N40" s="7" t="n"/>
-      <c r="O40" s="8" t="n"/>
+      <c r="N40" s="8" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="7" t="n"/>
-      <c r="B41" s="8" t="n"/>
+      <c r="B41" s="7" t="n"/>
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
@@ -1730,12 +1682,11 @@
       <c r="K41" s="8" t="n"/>
       <c r="L41" s="7" t="n"/>
       <c r="M41" s="7" t="n"/>
-      <c r="N41" s="7" t="n"/>
-      <c r="O41" s="8" t="n"/>
+      <c r="N41" s="8" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="7" t="n"/>
-      <c r="B42" s="8" t="n"/>
+      <c r="B42" s="7" t="n"/>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
@@ -1747,12 +1698,11 @@
       <c r="K42" s="8" t="n"/>
       <c r="L42" s="7" t="n"/>
       <c r="M42" s="7" t="n"/>
-      <c r="N42" s="7" t="n"/>
-      <c r="O42" s="8" t="n"/>
+      <c r="N42" s="8" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="7" t="n"/>
-      <c r="B43" s="8" t="n"/>
+      <c r="B43" s="7" t="n"/>
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
@@ -1764,12 +1714,11 @@
       <c r="K43" s="8" t="n"/>
       <c r="L43" s="7" t="n"/>
       <c r="M43" s="7" t="n"/>
-      <c r="N43" s="7" t="n"/>
-      <c r="O43" s="8" t="n"/>
+      <c r="N43" s="8" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="7" t="n"/>
-      <c r="B44" s="8" t="n"/>
+      <c r="B44" s="7" t="n"/>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
@@ -1781,12 +1730,11 @@
       <c r="K44" s="8" t="n"/>
       <c r="L44" s="7" t="n"/>
       <c r="M44" s="7" t="n"/>
-      <c r="N44" s="7" t="n"/>
-      <c r="O44" s="8" t="n"/>
+      <c r="N44" s="8" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="7" t="n"/>
-      <c r="B45" s="8" t="n"/>
+      <c r="B45" s="7" t="n"/>
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
@@ -1798,12 +1746,11 @@
       <c r="K45" s="8" t="n"/>
       <c r="L45" s="7" t="n"/>
       <c r="M45" s="7" t="n"/>
-      <c r="N45" s="7" t="n"/>
-      <c r="O45" s="8" t="n"/>
+      <c r="N45" s="8" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="7" t="n"/>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="7" t="n"/>
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
@@ -1815,12 +1762,11 @@
       <c r="K46" s="8" t="n"/>
       <c r="L46" s="7" t="n"/>
       <c r="M46" s="7" t="n"/>
-      <c r="N46" s="7" t="n"/>
-      <c r="O46" s="8" t="n"/>
+      <c r="N46" s="8" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="7" t="n"/>
-      <c r="B47" s="8" t="n"/>
+      <c r="B47" s="7" t="n"/>
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
@@ -1832,12 +1778,11 @@
       <c r="K47" s="8" t="n"/>
       <c r="L47" s="7" t="n"/>
       <c r="M47" s="7" t="n"/>
-      <c r="N47" s="7" t="n"/>
-      <c r="O47" s="8" t="n"/>
+      <c r="N47" s="8" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="7" t="n"/>
-      <c r="B48" s="8" t="n"/>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
@@ -1849,12 +1794,11 @@
       <c r="K48" s="8" t="n"/>
       <c r="L48" s="7" t="n"/>
       <c r="M48" s="7" t="n"/>
-      <c r="N48" s="7" t="n"/>
-      <c r="O48" s="8" t="n"/>
+      <c r="N48" s="8" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="7" t="n"/>
-      <c r="B49" s="8" t="n"/>
+      <c r="B49" s="7" t="n"/>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
@@ -1866,12 +1810,11 @@
       <c r="K49" s="8" t="n"/>
       <c r="L49" s="7" t="n"/>
       <c r="M49" s="7" t="n"/>
-      <c r="N49" s="7" t="n"/>
-      <c r="O49" s="8" t="n"/>
+      <c r="N49" s="8" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="7" t="n"/>
-      <c r="B50" s="8" t="n"/>
+      <c r="B50" s="7" t="n"/>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
@@ -1883,12 +1826,11 @@
       <c r="K50" s="8" t="n"/>
       <c r="L50" s="7" t="n"/>
       <c r="M50" s="7" t="n"/>
-      <c r="N50" s="7" t="n"/>
-      <c r="O50" s="8" t="n"/>
+      <c r="N50" s="8" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="7" t="n"/>
-      <c r="B51" s="8" t="n"/>
+      <c r="B51" s="7" t="n"/>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
@@ -1900,12 +1842,11 @@
       <c r="K51" s="8" t="n"/>
       <c r="L51" s="7" t="n"/>
       <c r="M51" s="7" t="n"/>
-      <c r="N51" s="7" t="n"/>
-      <c r="O51" s="8" t="n"/>
+      <c r="N51" s="8" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="7" t="n"/>
-      <c r="B52" s="8" t="n"/>
+      <c r="B52" s="7" t="n"/>
       <c r="C52" s="8" t="n"/>
       <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
@@ -1917,12 +1858,11 @@
       <c r="K52" s="8" t="n"/>
       <c r="L52" s="7" t="n"/>
       <c r="M52" s="7" t="n"/>
-      <c r="N52" s="7" t="n"/>
-      <c r="O52" s="8" t="n"/>
+      <c r="N52" s="8" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="7" t="n"/>
-      <c r="B53" s="8" t="n"/>
+      <c r="B53" s="7" t="n"/>
       <c r="C53" s="8" t="n"/>
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
@@ -1934,12 +1874,11 @@
       <c r="K53" s="8" t="n"/>
       <c r="L53" s="7" t="n"/>
       <c r="M53" s="7" t="n"/>
-      <c r="N53" s="7" t="n"/>
-      <c r="O53" s="8" t="n"/>
+      <c r="N53" s="8" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="7" t="n"/>
-      <c r="B54" s="8" t="n"/>
+      <c r="B54" s="7" t="n"/>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
@@ -1951,12 +1890,11 @@
       <c r="K54" s="8" t="n"/>
       <c r="L54" s="7" t="n"/>
       <c r="M54" s="7" t="n"/>
-      <c r="N54" s="7" t="n"/>
-      <c r="O54" s="8" t="n"/>
+      <c r="N54" s="8" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="7" t="n"/>
-      <c r="B55" s="8" t="n"/>
+      <c r="B55" s="7" t="n"/>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
@@ -1968,12 +1906,11 @@
       <c r="K55" s="8" t="n"/>
       <c r="L55" s="7" t="n"/>
       <c r="M55" s="7" t="n"/>
-      <c r="N55" s="7" t="n"/>
-      <c r="O55" s="8" t="n"/>
+      <c r="N55" s="8" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="7" t="n"/>
-      <c r="B56" s="8" t="n"/>
+      <c r="B56" s="7" t="n"/>
       <c r="C56" s="8" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
@@ -1985,12 +1922,11 @@
       <c r="K56" s="8" t="n"/>
       <c r="L56" s="7" t="n"/>
       <c r="M56" s="7" t="n"/>
-      <c r="N56" s="7" t="n"/>
-      <c r="O56" s="8" t="n"/>
+      <c r="N56" s="8" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="7" t="n"/>
-      <c r="B57" s="8" t="n"/>
+      <c r="B57" s="7" t="n"/>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
@@ -2002,12 +1938,11 @@
       <c r="K57" s="8" t="n"/>
       <c r="L57" s="7" t="n"/>
       <c r="M57" s="7" t="n"/>
-      <c r="N57" s="7" t="n"/>
-      <c r="O57" s="8" t="n"/>
+      <c r="N57" s="8" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="7" t="n"/>
-      <c r="B58" s="8" t="n"/>
+      <c r="B58" s="7" t="n"/>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
@@ -2019,12 +1954,11 @@
       <c r="K58" s="8" t="n"/>
       <c r="L58" s="7" t="n"/>
       <c r="M58" s="7" t="n"/>
-      <c r="N58" s="7" t="n"/>
-      <c r="O58" s="8" t="n"/>
+      <c r="N58" s="8" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="7" t="n"/>
-      <c r="B59" s="8" t="n"/>
+      <c r="B59" s="7" t="n"/>
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
@@ -2036,12 +1970,11 @@
       <c r="K59" s="8" t="n"/>
       <c r="L59" s="7" t="n"/>
       <c r="M59" s="7" t="n"/>
-      <c r="N59" s="7" t="n"/>
-      <c r="O59" s="8" t="n"/>
+      <c r="N59" s="8" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="7" t="n"/>
-      <c r="B60" s="8" t="n"/>
+      <c r="B60" s="7" t="n"/>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
@@ -2053,12 +1986,11 @@
       <c r="K60" s="8" t="n"/>
       <c r="L60" s="7" t="n"/>
       <c r="M60" s="7" t="n"/>
-      <c r="N60" s="7" t="n"/>
-      <c r="O60" s="8" t="n"/>
+      <c r="N60" s="8" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="7" t="n"/>
-      <c r="B61" s="8" t="n"/>
+      <c r="B61" s="7" t="n"/>
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
@@ -2070,12 +2002,11 @@
       <c r="K61" s="8" t="n"/>
       <c r="L61" s="7" t="n"/>
       <c r="M61" s="7" t="n"/>
-      <c r="N61" s="7" t="n"/>
-      <c r="O61" s="8" t="n"/>
+      <c r="N61" s="8" t="n"/>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="7" t="n"/>
-      <c r="B62" s="8" t="n"/>
+      <c r="B62" s="7" t="n"/>
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
@@ -2087,12 +2018,11 @@
       <c r="K62" s="8" t="n"/>
       <c r="L62" s="7" t="n"/>
       <c r="M62" s="7" t="n"/>
-      <c r="N62" s="7" t="n"/>
-      <c r="O62" s="8" t="n"/>
+      <c r="N62" s="8" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="7" t="n"/>
-      <c r="B63" s="8" t="n"/>
+      <c r="B63" s="7" t="n"/>
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
@@ -2104,12 +2034,11 @@
       <c r="K63" s="8" t="n"/>
       <c r="L63" s="7" t="n"/>
       <c r="M63" s="7" t="n"/>
-      <c r="N63" s="7" t="n"/>
-      <c r="O63" s="8" t="n"/>
+      <c r="N63" s="8" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="7" t="n"/>
-      <c r="B64" s="8" t="n"/>
+      <c r="B64" s="7" t="n"/>
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
@@ -2121,12 +2050,11 @@
       <c r="K64" s="8" t="n"/>
       <c r="L64" s="7" t="n"/>
       <c r="M64" s="7" t="n"/>
-      <c r="N64" s="7" t="n"/>
-      <c r="O64" s="8" t="n"/>
+      <c r="N64" s="8" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="7" t="n"/>
-      <c r="B65" s="8" t="n"/>
+      <c r="B65" s="7" t="n"/>
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
@@ -2138,12 +2066,11 @@
       <c r="K65" s="8" t="n"/>
       <c r="L65" s="7" t="n"/>
       <c r="M65" s="7" t="n"/>
-      <c r="N65" s="7" t="n"/>
-      <c r="O65" s="8" t="n"/>
+      <c r="N65" s="8" t="n"/>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="7" t="n"/>
-      <c r="B66" s="8" t="n"/>
+      <c r="B66" s="7" t="n"/>
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
@@ -2155,12 +2082,11 @@
       <c r="K66" s="8" t="n"/>
       <c r="L66" s="7" t="n"/>
       <c r="M66" s="7" t="n"/>
-      <c r="N66" s="7" t="n"/>
-      <c r="O66" s="8" t="n"/>
+      <c r="N66" s="8" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="7" t="n"/>
-      <c r="B67" s="8" t="n"/>
+      <c r="B67" s="7" t="n"/>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
@@ -2172,12 +2098,11 @@
       <c r="K67" s="8" t="n"/>
       <c r="L67" s="7" t="n"/>
       <c r="M67" s="7" t="n"/>
-      <c r="N67" s="7" t="n"/>
-      <c r="O67" s="8" t="n"/>
+      <c r="N67" s="8" t="n"/>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="7" t="n"/>
-      <c r="B68" s="8" t="n"/>
+      <c r="B68" s="7" t="n"/>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
@@ -2189,12 +2114,11 @@
       <c r="K68" s="8" t="n"/>
       <c r="L68" s="7" t="n"/>
       <c r="M68" s="7" t="n"/>
-      <c r="N68" s="7" t="n"/>
-      <c r="O68" s="8" t="n"/>
+      <c r="N68" s="8" t="n"/>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="7" t="n"/>
-      <c r="B69" s="8" t="n"/>
+      <c r="B69" s="7" t="n"/>
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
@@ -2206,12 +2130,11 @@
       <c r="K69" s="8" t="n"/>
       <c r="L69" s="7" t="n"/>
       <c r="M69" s="7" t="n"/>
-      <c r="N69" s="7" t="n"/>
-      <c r="O69" s="8" t="n"/>
+      <c r="N69" s="8" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="7" t="n"/>
-      <c r="B70" s="8" t="n"/>
+      <c r="B70" s="7" t="n"/>
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
@@ -2223,12 +2146,11 @@
       <c r="K70" s="8" t="n"/>
       <c r="L70" s="7" t="n"/>
       <c r="M70" s="7" t="n"/>
-      <c r="N70" s="7" t="n"/>
-      <c r="O70" s="8" t="n"/>
+      <c r="N70" s="8" t="n"/>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="7" t="n"/>
-      <c r="B71" s="8" t="n"/>
+      <c r="B71" s="7" t="n"/>
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
@@ -2240,12 +2162,11 @@
       <c r="K71" s="8" t="n"/>
       <c r="L71" s="7" t="n"/>
       <c r="M71" s="7" t="n"/>
-      <c r="N71" s="7" t="n"/>
-      <c r="O71" s="8" t="n"/>
+      <c r="N71" s="8" t="n"/>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="7" t="n"/>
-      <c r="B72" s="8" t="n"/>
+      <c r="B72" s="7" t="n"/>
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
@@ -2257,12 +2178,11 @@
       <c r="K72" s="8" t="n"/>
       <c r="L72" s="7" t="n"/>
       <c r="M72" s="7" t="n"/>
-      <c r="N72" s="7" t="n"/>
-      <c r="O72" s="8" t="n"/>
+      <c r="N72" s="8" t="n"/>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="7" t="n"/>
-      <c r="B73" s="8" t="n"/>
+      <c r="B73" s="7" t="n"/>
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
@@ -2274,12 +2194,11 @@
       <c r="K73" s="8" t="n"/>
       <c r="L73" s="7" t="n"/>
       <c r="M73" s="7" t="n"/>
-      <c r="N73" s="7" t="n"/>
-      <c r="O73" s="8" t="n"/>
+      <c r="N73" s="8" t="n"/>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="7" t="n"/>
-      <c r="B74" s="8" t="n"/>
+      <c r="B74" s="7" t="n"/>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
@@ -2291,12 +2210,11 @@
       <c r="K74" s="8" t="n"/>
       <c r="L74" s="7" t="n"/>
       <c r="M74" s="7" t="n"/>
-      <c r="N74" s="7" t="n"/>
-      <c r="O74" s="8" t="n"/>
+      <c r="N74" s="8" t="n"/>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="7" t="n"/>
-      <c r="B75" s="8" t="n"/>
+      <c r="B75" s="7" t="n"/>
       <c r="C75" s="8" t="n"/>
       <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
@@ -2308,12 +2226,11 @@
       <c r="K75" s="8" t="n"/>
       <c r="L75" s="7" t="n"/>
       <c r="M75" s="7" t="n"/>
-      <c r="N75" s="7" t="n"/>
-      <c r="O75" s="8" t="n"/>
+      <c r="N75" s="8" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="7" t="n"/>
-      <c r="B76" s="8" t="n"/>
+      <c r="B76" s="7" t="n"/>
       <c r="C76" s="8" t="n"/>
       <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
@@ -2325,12 +2242,11 @@
       <c r="K76" s="8" t="n"/>
       <c r="L76" s="7" t="n"/>
       <c r="M76" s="7" t="n"/>
-      <c r="N76" s="7" t="n"/>
-      <c r="O76" s="8" t="n"/>
+      <c r="N76" s="8" t="n"/>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="7" t="n"/>
-      <c r="B77" s="8" t="n"/>
+      <c r="B77" s="7" t="n"/>
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
@@ -2342,12 +2258,11 @@
       <c r="K77" s="8" t="n"/>
       <c r="L77" s="7" t="n"/>
       <c r="M77" s="7" t="n"/>
-      <c r="N77" s="7" t="n"/>
-      <c r="O77" s="8" t="n"/>
+      <c r="N77" s="8" t="n"/>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="7" t="n"/>
-      <c r="B78" s="8" t="n"/>
+      <c r="B78" s="7" t="n"/>
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="7" t="n"/>
       <c r="E78" s="7" t="n"/>
@@ -2359,12 +2274,11 @@
       <c r="K78" s="8" t="n"/>
       <c r="L78" s="7" t="n"/>
       <c r="M78" s="7" t="n"/>
-      <c r="N78" s="7" t="n"/>
-      <c r="O78" s="8" t="n"/>
+      <c r="N78" s="8" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="7" t="n"/>
-      <c r="B79" s="8" t="n"/>
+      <c r="B79" s="7" t="n"/>
       <c r="C79" s="8" t="n"/>
       <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
@@ -2376,12 +2290,11 @@
       <c r="K79" s="8" t="n"/>
       <c r="L79" s="7" t="n"/>
       <c r="M79" s="7" t="n"/>
-      <c r="N79" s="7" t="n"/>
-      <c r="O79" s="8" t="n"/>
+      <c r="N79" s="8" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="7" t="n"/>
-      <c r="B80" s="8" t="n"/>
+      <c r="B80" s="7" t="n"/>
       <c r="C80" s="8" t="n"/>
       <c r="D80" s="7" t="n"/>
       <c r="E80" s="7" t="n"/>
@@ -2393,12 +2306,11 @@
       <c r="K80" s="8" t="n"/>
       <c r="L80" s="7" t="n"/>
       <c r="M80" s="7" t="n"/>
-      <c r="N80" s="7" t="n"/>
-      <c r="O80" s="8" t="n"/>
+      <c r="N80" s="8" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="7" t="n"/>
-      <c r="B81" s="8" t="n"/>
+      <c r="B81" s="7" t="n"/>
       <c r="C81" s="8" t="n"/>
       <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
@@ -2410,12 +2322,11 @@
       <c r="K81" s="8" t="n"/>
       <c r="L81" s="7" t="n"/>
       <c r="M81" s="7" t="n"/>
-      <c r="N81" s="7" t="n"/>
-      <c r="O81" s="8" t="n"/>
+      <c r="N81" s="8" t="n"/>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="7" t="n"/>
-      <c r="B82" s="8" t="n"/>
+      <c r="B82" s="7" t="n"/>
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
@@ -2427,12 +2338,11 @@
       <c r="K82" s="8" t="n"/>
       <c r="L82" s="7" t="n"/>
       <c r="M82" s="7" t="n"/>
-      <c r="N82" s="7" t="n"/>
-      <c r="O82" s="8" t="n"/>
+      <c r="N82" s="8" t="n"/>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="7" t="n"/>
-      <c r="B83" s="8" t="n"/>
+      <c r="B83" s="7" t="n"/>
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="7" t="n"/>
       <c r="E83" s="7" t="n"/>
@@ -2444,12 +2354,11 @@
       <c r="K83" s="8" t="n"/>
       <c r="L83" s="7" t="n"/>
       <c r="M83" s="7" t="n"/>
-      <c r="N83" s="7" t="n"/>
-      <c r="O83" s="8" t="n"/>
+      <c r="N83" s="8" t="n"/>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="7" t="n"/>
-      <c r="B84" s="8" t="n"/>
+      <c r="B84" s="7" t="n"/>
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="7" t="n"/>
       <c r="E84" s="7" t="n"/>
@@ -2461,12 +2370,11 @@
       <c r="K84" s="8" t="n"/>
       <c r="L84" s="7" t="n"/>
       <c r="M84" s="7" t="n"/>
-      <c r="N84" s="7" t="n"/>
-      <c r="O84" s="8" t="n"/>
+      <c r="N84" s="8" t="n"/>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="7" t="n"/>
-      <c r="B85" s="8" t="n"/>
+      <c r="B85" s="7" t="n"/>
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="7" t="n"/>
       <c r="E85" s="7" t="n"/>
@@ -2478,12 +2386,11 @@
       <c r="K85" s="8" t="n"/>
       <c r="L85" s="7" t="n"/>
       <c r="M85" s="7" t="n"/>
-      <c r="N85" s="7" t="n"/>
-      <c r="O85" s="8" t="n"/>
+      <c r="N85" s="8" t="n"/>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="7" t="n"/>
-      <c r="B86" s="8" t="n"/>
+      <c r="B86" s="7" t="n"/>
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="7" t="n"/>
       <c r="E86" s="7" t="n"/>
@@ -2495,12 +2402,11 @@
       <c r="K86" s="8" t="n"/>
       <c r="L86" s="7" t="n"/>
       <c r="M86" s="7" t="n"/>
-      <c r="N86" s="7" t="n"/>
-      <c r="O86" s="8" t="n"/>
+      <c r="N86" s="8" t="n"/>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="7" t="n"/>
-      <c r="B87" s="8" t="n"/>
+      <c r="B87" s="7" t="n"/>
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="7" t="n"/>
       <c r="E87" s="7" t="n"/>
@@ -2512,12 +2418,11 @@
       <c r="K87" s="8" t="n"/>
       <c r="L87" s="7" t="n"/>
       <c r="M87" s="7" t="n"/>
-      <c r="N87" s="7" t="n"/>
-      <c r="O87" s="8" t="n"/>
+      <c r="N87" s="8" t="n"/>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="7" t="n"/>
-      <c r="B88" s="8" t="n"/>
+      <c r="B88" s="7" t="n"/>
       <c r="C88" s="8" t="n"/>
       <c r="D88" s="7" t="n"/>
       <c r="E88" s="7" t="n"/>
@@ -2529,12 +2434,11 @@
       <c r="K88" s="8" t="n"/>
       <c r="L88" s="7" t="n"/>
       <c r="M88" s="7" t="n"/>
-      <c r="N88" s="7" t="n"/>
-      <c r="O88" s="8" t="n"/>
+      <c r="N88" s="8" t="n"/>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="7" t="n"/>
-      <c r="B89" s="8" t="n"/>
+      <c r="B89" s="7" t="n"/>
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
@@ -2546,12 +2450,11 @@
       <c r="K89" s="8" t="n"/>
       <c r="L89" s="7" t="n"/>
       <c r="M89" s="7" t="n"/>
-      <c r="N89" s="7" t="n"/>
-      <c r="O89" s="8" t="n"/>
+      <c r="N89" s="8" t="n"/>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="7" t="n"/>
-      <c r="B90" s="8" t="n"/>
+      <c r="B90" s="7" t="n"/>
       <c r="C90" s="8" t="n"/>
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
@@ -2563,12 +2466,11 @@
       <c r="K90" s="8" t="n"/>
       <c r="L90" s="7" t="n"/>
       <c r="M90" s="7" t="n"/>
-      <c r="N90" s="7" t="n"/>
-      <c r="O90" s="8" t="n"/>
+      <c r="N90" s="8" t="n"/>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="7" t="n"/>
-      <c r="B91" s="8" t="n"/>
+      <c r="B91" s="7" t="n"/>
       <c r="C91" s="8" t="n"/>
       <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
@@ -2580,12 +2482,11 @@
       <c r="K91" s="8" t="n"/>
       <c r="L91" s="7" t="n"/>
       <c r="M91" s="7" t="n"/>
-      <c r="N91" s="7" t="n"/>
-      <c r="O91" s="8" t="n"/>
+      <c r="N91" s="8" t="n"/>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="7" t="n"/>
-      <c r="B92" s="8" t="n"/>
+      <c r="B92" s="7" t="n"/>
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
@@ -2597,12 +2498,11 @@
       <c r="K92" s="8" t="n"/>
       <c r="L92" s="7" t="n"/>
       <c r="M92" s="7" t="n"/>
-      <c r="N92" s="7" t="n"/>
-      <c r="O92" s="8" t="n"/>
+      <c r="N92" s="8" t="n"/>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="7" t="n"/>
-      <c r="B93" s="8" t="n"/>
+      <c r="B93" s="7" t="n"/>
       <c r="C93" s="8" t="n"/>
       <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
@@ -2614,12 +2514,11 @@
       <c r="K93" s="8" t="n"/>
       <c r="L93" s="7" t="n"/>
       <c r="M93" s="7" t="n"/>
-      <c r="N93" s="7" t="n"/>
-      <c r="O93" s="8" t="n"/>
+      <c r="N93" s="8" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="7" t="n"/>
-      <c r="B94" s="8" t="n"/>
+      <c r="B94" s="7" t="n"/>
       <c r="C94" s="8" t="n"/>
       <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
@@ -2631,12 +2530,11 @@
       <c r="K94" s="8" t="n"/>
       <c r="L94" s="7" t="n"/>
       <c r="M94" s="7" t="n"/>
-      <c r="N94" s="7" t="n"/>
-      <c r="O94" s="8" t="n"/>
+      <c r="N94" s="8" t="n"/>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="7" t="n"/>
-      <c r="B95" s="8" t="n"/>
+      <c r="B95" s="7" t="n"/>
       <c r="C95" s="8" t="n"/>
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
@@ -2648,12 +2546,11 @@
       <c r="K95" s="8" t="n"/>
       <c r="L95" s="7" t="n"/>
       <c r="M95" s="7" t="n"/>
-      <c r="N95" s="7" t="n"/>
-      <c r="O95" s="8" t="n"/>
+      <c r="N95" s="8" t="n"/>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="7" t="n"/>
-      <c r="B96" s="8" t="n"/>
+      <c r="B96" s="7" t="n"/>
       <c r="C96" s="8" t="n"/>
       <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
@@ -2665,12 +2562,11 @@
       <c r="K96" s="8" t="n"/>
       <c r="L96" s="7" t="n"/>
       <c r="M96" s="7" t="n"/>
-      <c r="N96" s="7" t="n"/>
-      <c r="O96" s="8" t="n"/>
+      <c r="N96" s="8" t="n"/>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="7" t="n"/>
-      <c r="B97" s="8" t="n"/>
+      <c r="B97" s="7" t="n"/>
       <c r="C97" s="8" t="n"/>
       <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
@@ -2682,12 +2578,11 @@
       <c r="K97" s="8" t="n"/>
       <c r="L97" s="7" t="n"/>
       <c r="M97" s="7" t="n"/>
-      <c r="N97" s="7" t="n"/>
-      <c r="O97" s="8" t="n"/>
+      <c r="N97" s="8" t="n"/>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="7" t="n"/>
-      <c r="B98" s="8" t="n"/>
+      <c r="B98" s="7" t="n"/>
       <c r="C98" s="8" t="n"/>
       <c r="D98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
@@ -2699,12 +2594,11 @@
       <c r="K98" s="8" t="n"/>
       <c r="L98" s="7" t="n"/>
       <c r="M98" s="7" t="n"/>
-      <c r="N98" s="7" t="n"/>
-      <c r="O98" s="8" t="n"/>
+      <c r="N98" s="8" t="n"/>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="7" t="n"/>
-      <c r="B99" s="8" t="n"/>
+      <c r="B99" s="7" t="n"/>
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
@@ -2716,12 +2610,11 @@
       <c r="K99" s="8" t="n"/>
       <c r="L99" s="7" t="n"/>
       <c r="M99" s="7" t="n"/>
-      <c r="N99" s="7" t="n"/>
-      <c r="O99" s="8" t="n"/>
+      <c r="N99" s="8" t="n"/>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="7" t="n"/>
-      <c r="B100" s="8" t="n"/>
+      <c r="B100" s="7" t="n"/>
       <c r="C100" s="8" t="n"/>
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
@@ -2733,12 +2626,11 @@
       <c r="K100" s="8" t="n"/>
       <c r="L100" s="7" t="n"/>
       <c r="M100" s="7" t="n"/>
-      <c r="N100" s="7" t="n"/>
-      <c r="O100" s="8" t="n"/>
+      <c r="N100" s="8" t="n"/>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="7" t="n"/>
-      <c r="B101" s="8" t="n"/>
+      <c r="B101" s="7" t="n"/>
       <c r="C101" s="8" t="n"/>
       <c r="D101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
@@ -2750,12 +2642,11 @@
       <c r="K101" s="8" t="n"/>
       <c r="L101" s="7" t="n"/>
       <c r="M101" s="7" t="n"/>
-      <c r="N101" s="7" t="n"/>
-      <c r="O101" s="8" t="n"/>
+      <c r="N101" s="8" t="n"/>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="7" t="n"/>
-      <c r="B102" s="8" t="n"/>
+      <c r="B102" s="7" t="n"/>
       <c r="C102" s="8" t="n"/>
       <c r="D102" s="7" t="n"/>
       <c r="E102" s="7" t="n"/>
@@ -2767,12 +2658,11 @@
       <c r="K102" s="8" t="n"/>
       <c r="L102" s="7" t="n"/>
       <c r="M102" s="7" t="n"/>
-      <c r="N102" s="7" t="n"/>
-      <c r="O102" s="8" t="n"/>
+      <c r="N102" s="8" t="n"/>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="7" t="n"/>
-      <c r="B103" s="8" t="n"/>
+      <c r="B103" s="7" t="n"/>
       <c r="C103" s="8" t="n"/>
       <c r="D103" s="7" t="n"/>
       <c r="E103" s="7" t="n"/>
@@ -2784,12 +2674,11 @@
       <c r="K103" s="8" t="n"/>
       <c r="L103" s="7" t="n"/>
       <c r="M103" s="7" t="n"/>
-      <c r="N103" s="7" t="n"/>
-      <c r="O103" s="8" t="n"/>
+      <c r="N103" s="8" t="n"/>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="7" t="n"/>
-      <c r="B104" s="8" t="n"/>
+      <c r="B104" s="7" t="n"/>
       <c r="C104" s="8" t="n"/>
       <c r="D104" s="7" t="n"/>
       <c r="E104" s="7" t="n"/>
@@ -2801,12 +2690,11 @@
       <c r="K104" s="8" t="n"/>
       <c r="L104" s="7" t="n"/>
       <c r="M104" s="7" t="n"/>
-      <c r="N104" s="7" t="n"/>
-      <c r="O104" s="8" t="n"/>
+      <c r="N104" s="8" t="n"/>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="7" t="n"/>
-      <c r="B105" s="8" t="n"/>
+      <c r="B105" s="7" t="n"/>
       <c r="C105" s="8" t="n"/>
       <c r="D105" s="7" t="n"/>
       <c r="E105" s="7" t="n"/>
@@ -2818,12 +2706,11 @@
       <c r="K105" s="8" t="n"/>
       <c r="L105" s="7" t="n"/>
       <c r="M105" s="7" t="n"/>
-      <c r="N105" s="7" t="n"/>
-      <c r="O105" s="8" t="n"/>
+      <c r="N105" s="8" t="n"/>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="7" t="n"/>
-      <c r="B106" s="8" t="n"/>
+      <c r="B106" s="7" t="n"/>
       <c r="C106" s="8" t="n"/>
       <c r="D106" s="7" t="n"/>
       <c r="E106" s="7" t="n"/>
@@ -2835,12 +2722,11 @@
       <c r="K106" s="8" t="n"/>
       <c r="L106" s="7" t="n"/>
       <c r="M106" s="7" t="n"/>
-      <c r="N106" s="7" t="n"/>
-      <c r="O106" s="8" t="n"/>
+      <c r="N106" s="8" t="n"/>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="7" t="n"/>
-      <c r="B107" s="8" t="n"/>
+      <c r="B107" s="7" t="n"/>
       <c r="C107" s="8" t="n"/>
       <c r="D107" s="7" t="n"/>
       <c r="E107" s="7" t="n"/>
@@ -2852,12 +2738,11 @@
       <c r="K107" s="8" t="n"/>
       <c r="L107" s="7" t="n"/>
       <c r="M107" s="7" t="n"/>
-      <c r="N107" s="7" t="n"/>
-      <c r="O107" s="8" t="n"/>
+      <c r="N107" s="8" t="n"/>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="7" t="n"/>
-      <c r="B108" s="8" t="n"/>
+      <c r="B108" s="7" t="n"/>
       <c r="C108" s="8" t="n"/>
       <c r="D108" s="7" t="n"/>
       <c r="E108" s="7" t="n"/>
@@ -2869,12 +2754,11 @@
       <c r="K108" s="8" t="n"/>
       <c r="L108" s="7" t="n"/>
       <c r="M108" s="7" t="n"/>
-      <c r="N108" s="7" t="n"/>
-      <c r="O108" s="8" t="n"/>
+      <c r="N108" s="8" t="n"/>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="7" t="n"/>
-      <c r="B109" s="8" t="n"/>
+      <c r="B109" s="7" t="n"/>
       <c r="C109" s="8" t="n"/>
       <c r="D109" s="7" t="n"/>
       <c r="E109" s="7" t="n"/>
@@ -2886,12 +2770,11 @@
       <c r="K109" s="8" t="n"/>
       <c r="L109" s="7" t="n"/>
       <c r="M109" s="7" t="n"/>
-      <c r="N109" s="7" t="n"/>
-      <c r="O109" s="8" t="n"/>
+      <c r="N109" s="8" t="n"/>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="7" t="n"/>
-      <c r="B110" s="8" t="n"/>
+      <c r="B110" s="7" t="n"/>
       <c r="C110" s="8" t="n"/>
       <c r="D110" s="7" t="n"/>
       <c r="E110" s="7" t="n"/>
@@ -2903,12 +2786,11 @@
       <c r="K110" s="8" t="n"/>
       <c r="L110" s="7" t="n"/>
       <c r="M110" s="7" t="n"/>
-      <c r="N110" s="7" t="n"/>
-      <c r="O110" s="8" t="n"/>
+      <c r="N110" s="8" t="n"/>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="7" t="n"/>
-      <c r="B111" s="8" t="n"/>
+      <c r="B111" s="7" t="n"/>
       <c r="C111" s="8" t="n"/>
       <c r="D111" s="7" t="n"/>
       <c r="E111" s="7" t="n"/>
@@ -2920,12 +2802,11 @@
       <c r="K111" s="8" t="n"/>
       <c r="L111" s="7" t="n"/>
       <c r="M111" s="7" t="n"/>
-      <c r="N111" s="7" t="n"/>
-      <c r="O111" s="8" t="n"/>
+      <c r="N111" s="8" t="n"/>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="7" t="n"/>
-      <c r="B112" s="8" t="n"/>
+      <c r="B112" s="7" t="n"/>
       <c r="C112" s="8" t="n"/>
       <c r="D112" s="7" t="n"/>
       <c r="E112" s="7" t="n"/>
@@ -2937,12 +2818,11 @@
       <c r="K112" s="8" t="n"/>
       <c r="L112" s="7" t="n"/>
       <c r="M112" s="7" t="n"/>
-      <c r="N112" s="7" t="n"/>
-      <c r="O112" s="8" t="n"/>
+      <c r="N112" s="8" t="n"/>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="7" t="n"/>
-      <c r="B113" s="8" t="n"/>
+      <c r="B113" s="7" t="n"/>
       <c r="C113" s="8" t="n"/>
       <c r="D113" s="7" t="n"/>
       <c r="E113" s="7" t="n"/>
@@ -2954,12 +2834,11 @@
       <c r="K113" s="8" t="n"/>
       <c r="L113" s="7" t="n"/>
       <c r="M113" s="7" t="n"/>
-      <c r="N113" s="7" t="n"/>
-      <c r="O113" s="8" t="n"/>
+      <c r="N113" s="8" t="n"/>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="7" t="n"/>
-      <c r="B114" s="8" t="n"/>
+      <c r="B114" s="7" t="n"/>
       <c r="C114" s="8" t="n"/>
       <c r="D114" s="7" t="n"/>
       <c r="E114" s="7" t="n"/>
@@ -2971,12 +2850,11 @@
       <c r="K114" s="8" t="n"/>
       <c r="L114" s="7" t="n"/>
       <c r="M114" s="7" t="n"/>
-      <c r="N114" s="7" t="n"/>
-      <c r="O114" s="8" t="n"/>
+      <c r="N114" s="8" t="n"/>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="7" t="n"/>
-      <c r="B115" s="8" t="n"/>
+      <c r="B115" s="7" t="n"/>
       <c r="C115" s="8" t="n"/>
       <c r="D115" s="7" t="n"/>
       <c r="E115" s="7" t="n"/>
@@ -2988,12 +2866,11 @@
       <c r="K115" s="8" t="n"/>
       <c r="L115" s="7" t="n"/>
       <c r="M115" s="7" t="n"/>
-      <c r="N115" s="7" t="n"/>
-      <c r="O115" s="8" t="n"/>
+      <c r="N115" s="8" t="n"/>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="7" t="n"/>
-      <c r="B116" s="8" t="n"/>
+      <c r="B116" s="7" t="n"/>
       <c r="C116" s="8" t="n"/>
       <c r="D116" s="7" t="n"/>
       <c r="E116" s="7" t="n"/>
@@ -3005,12 +2882,11 @@
       <c r="K116" s="8" t="n"/>
       <c r="L116" s="7" t="n"/>
       <c r="M116" s="7" t="n"/>
-      <c r="N116" s="7" t="n"/>
-      <c r="O116" s="8" t="n"/>
+      <c r="N116" s="8" t="n"/>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="7" t="n"/>
-      <c r="B117" s="8" t="n"/>
+      <c r="B117" s="7" t="n"/>
       <c r="C117" s="8" t="n"/>
       <c r="D117" s="7" t="n"/>
       <c r="E117" s="7" t="n"/>
@@ -3022,12 +2898,11 @@
       <c r="K117" s="8" t="n"/>
       <c r="L117" s="7" t="n"/>
       <c r="M117" s="7" t="n"/>
-      <c r="N117" s="7" t="n"/>
-      <c r="O117" s="8" t="n"/>
+      <c r="N117" s="8" t="n"/>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="7" t="n"/>
-      <c r="B118" s="8" t="n"/>
+      <c r="B118" s="7" t="n"/>
       <c r="C118" s="8" t="n"/>
       <c r="D118" s="7" t="n"/>
       <c r="E118" s="7" t="n"/>
@@ -3039,12 +2914,11 @@
       <c r="K118" s="8" t="n"/>
       <c r="L118" s="7" t="n"/>
       <c r="M118" s="7" t="n"/>
-      <c r="N118" s="7" t="n"/>
-      <c r="O118" s="8" t="n"/>
+      <c r="N118" s="8" t="n"/>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="7" t="n"/>
-      <c r="B119" s="8" t="n"/>
+      <c r="B119" s="7" t="n"/>
       <c r="C119" s="8" t="n"/>
       <c r="D119" s="7" t="n"/>
       <c r="E119" s="7" t="n"/>
@@ -3056,12 +2930,11 @@
       <c r="K119" s="8" t="n"/>
       <c r="L119" s="7" t="n"/>
       <c r="M119" s="7" t="n"/>
-      <c r="N119" s="7" t="n"/>
-      <c r="O119" s="8" t="n"/>
+      <c r="N119" s="8" t="n"/>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="7" t="n"/>
-      <c r="B120" s="8" t="n"/>
+      <c r="B120" s="7" t="n"/>
       <c r="C120" s="8" t="n"/>
       <c r="D120" s="7" t="n"/>
       <c r="E120" s="7" t="n"/>
@@ -3073,12 +2946,11 @@
       <c r="K120" s="8" t="n"/>
       <c r="L120" s="7" t="n"/>
       <c r="M120" s="7" t="n"/>
-      <c r="N120" s="7" t="n"/>
-      <c r="O120" s="8" t="n"/>
+      <c r="N120" s="8" t="n"/>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="7" t="n"/>
-      <c r="B121" s="8" t="n"/>
+      <c r="B121" s="7" t="n"/>
       <c r="C121" s="8" t="n"/>
       <c r="D121" s="7" t="n"/>
       <c r="E121" s="7" t="n"/>
@@ -3090,12 +2962,11 @@
       <c r="K121" s="8" t="n"/>
       <c r="L121" s="7" t="n"/>
       <c r="M121" s="7" t="n"/>
-      <c r="N121" s="7" t="n"/>
-      <c r="O121" s="8" t="n"/>
+      <c r="N121" s="8" t="n"/>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="7" t="n"/>
-      <c r="B122" s="8" t="n"/>
+      <c r="B122" s="7" t="n"/>
       <c r="C122" s="8" t="n"/>
       <c r="D122" s="7" t="n"/>
       <c r="E122" s="7" t="n"/>
@@ -3107,12 +2978,11 @@
       <c r="K122" s="8" t="n"/>
       <c r="L122" s="7" t="n"/>
       <c r="M122" s="7" t="n"/>
-      <c r="N122" s="7" t="n"/>
-      <c r="O122" s="8" t="n"/>
+      <c r="N122" s="8" t="n"/>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="7" t="n"/>
-      <c r="B123" s="8" t="n"/>
+      <c r="B123" s="7" t="n"/>
       <c r="C123" s="8" t="n"/>
       <c r="D123" s="7" t="n"/>
       <c r="E123" s="7" t="n"/>
@@ -3124,12 +2994,11 @@
       <c r="K123" s="8" t="n"/>
       <c r="L123" s="7" t="n"/>
       <c r="M123" s="7" t="n"/>
-      <c r="N123" s="7" t="n"/>
-      <c r="O123" s="8" t="n"/>
+      <c r="N123" s="8" t="n"/>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="7" t="n"/>
-      <c r="B124" s="8" t="n"/>
+      <c r="B124" s="7" t="n"/>
       <c r="C124" s="8" t="n"/>
       <c r="D124" s="7" t="n"/>
       <c r="E124" s="7" t="n"/>
@@ -3141,12 +3010,11 @@
       <c r="K124" s="8" t="n"/>
       <c r="L124" s="7" t="n"/>
       <c r="M124" s="7" t="n"/>
-      <c r="N124" s="7" t="n"/>
-      <c r="O124" s="8" t="n"/>
+      <c r="N124" s="8" t="n"/>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="7" t="n"/>
-      <c r="B125" s="8" t="n"/>
+      <c r="B125" s="7" t="n"/>
       <c r="C125" s="8" t="n"/>
       <c r="D125" s="7" t="n"/>
       <c r="E125" s="7" t="n"/>
@@ -3158,12 +3026,11 @@
       <c r="K125" s="8" t="n"/>
       <c r="L125" s="7" t="n"/>
       <c r="M125" s="7" t="n"/>
-      <c r="N125" s="7" t="n"/>
-      <c r="O125" s="8" t="n"/>
+      <c r="N125" s="8" t="n"/>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="7" t="n"/>
-      <c r="B126" s="8" t="n"/>
+      <c r="B126" s="7" t="n"/>
       <c r="C126" s="8" t="n"/>
       <c r="D126" s="7" t="n"/>
       <c r="E126" s="7" t="n"/>
@@ -3175,12 +3042,11 @@
       <c r="K126" s="8" t="n"/>
       <c r="L126" s="7" t="n"/>
       <c r="M126" s="7" t="n"/>
-      <c r="N126" s="7" t="n"/>
-      <c r="O126" s="8" t="n"/>
+      <c r="N126" s="8" t="n"/>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="7" t="n"/>
-      <c r="B127" s="8" t="n"/>
+      <c r="B127" s="7" t="n"/>
       <c r="C127" s="8" t="n"/>
       <c r="D127" s="7" t="n"/>
       <c r="E127" s="7" t="n"/>
@@ -3192,12 +3058,11 @@
       <c r="K127" s="8" t="n"/>
       <c r="L127" s="7" t="n"/>
       <c r="M127" s="7" t="n"/>
-      <c r="N127" s="7" t="n"/>
-      <c r="O127" s="8" t="n"/>
+      <c r="N127" s="8" t="n"/>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="7" t="n"/>
-      <c r="B128" s="8" t="n"/>
+      <c r="B128" s="7" t="n"/>
       <c r="C128" s="8" t="n"/>
       <c r="D128" s="7" t="n"/>
       <c r="E128" s="7" t="n"/>
@@ -3209,12 +3074,11 @@
       <c r="K128" s="8" t="n"/>
       <c r="L128" s="7" t="n"/>
       <c r="M128" s="7" t="n"/>
-      <c r="N128" s="7" t="n"/>
-      <c r="O128" s="8" t="n"/>
+      <c r="N128" s="8" t="n"/>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="7" t="n"/>
-      <c r="B129" s="8" t="n"/>
+      <c r="B129" s="7" t="n"/>
       <c r="C129" s="8" t="n"/>
       <c r="D129" s="7" t="n"/>
       <c r="E129" s="7" t="n"/>
@@ -3226,12 +3090,11 @@
       <c r="K129" s="8" t="n"/>
       <c r="L129" s="7" t="n"/>
       <c r="M129" s="7" t="n"/>
-      <c r="N129" s="7" t="n"/>
-      <c r="O129" s="8" t="n"/>
+      <c r="N129" s="8" t="n"/>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="7" t="n"/>
-      <c r="B130" s="8" t="n"/>
+      <c r="B130" s="7" t="n"/>
       <c r="C130" s="8" t="n"/>
       <c r="D130" s="7" t="n"/>
       <c r="E130" s="7" t="n"/>
@@ -3243,12 +3106,11 @@
       <c r="K130" s="8" t="n"/>
       <c r="L130" s="7" t="n"/>
       <c r="M130" s="7" t="n"/>
-      <c r="N130" s="7" t="n"/>
-      <c r="O130" s="8" t="n"/>
+      <c r="N130" s="8" t="n"/>
     </row>
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="7" t="n"/>
-      <c r="B131" s="8" t="n"/>
+      <c r="B131" s="7" t="n"/>
       <c r="C131" s="8" t="n"/>
       <c r="D131" s="7" t="n"/>
       <c r="E131" s="7" t="n"/>
@@ -3260,12 +3122,11 @@
       <c r="K131" s="8" t="n"/>
       <c r="L131" s="7" t="n"/>
       <c r="M131" s="7" t="n"/>
-      <c r="N131" s="7" t="n"/>
-      <c r="O131" s="8" t="n"/>
+      <c r="N131" s="8" t="n"/>
     </row>
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="7" t="n"/>
-      <c r="B132" s="8" t="n"/>
+      <c r="B132" s="7" t="n"/>
       <c r="C132" s="8" t="n"/>
       <c r="D132" s="7" t="n"/>
       <c r="E132" s="7" t="n"/>
@@ -3277,12 +3138,11 @@
       <c r="K132" s="8" t="n"/>
       <c r="L132" s="7" t="n"/>
       <c r="M132" s="7" t="n"/>
-      <c r="N132" s="7" t="n"/>
-      <c r="O132" s="8" t="n"/>
+      <c r="N132" s="8" t="n"/>
     </row>
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="7" t="n"/>
-      <c r="B133" s="8" t="n"/>
+      <c r="B133" s="7" t="n"/>
       <c r="C133" s="8" t="n"/>
       <c r="D133" s="7" t="n"/>
       <c r="E133" s="7" t="n"/>
@@ -3294,12 +3154,11 @@
       <c r="K133" s="8" t="n"/>
       <c r="L133" s="7" t="n"/>
       <c r="M133" s="7" t="n"/>
-      <c r="N133" s="7" t="n"/>
-      <c r="O133" s="8" t="n"/>
+      <c r="N133" s="8" t="n"/>
     </row>
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="7" t="n"/>
-      <c r="B134" s="8" t="n"/>
+      <c r="B134" s="7" t="n"/>
       <c r="C134" s="8" t="n"/>
       <c r="D134" s="7" t="n"/>
       <c r="E134" s="7" t="n"/>
@@ -3311,12 +3170,11 @@
       <c r="K134" s="8" t="n"/>
       <c r="L134" s="7" t="n"/>
       <c r="M134" s="7" t="n"/>
-      <c r="N134" s="7" t="n"/>
-      <c r="O134" s="8" t="n"/>
+      <c r="N134" s="8" t="n"/>
     </row>
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="7" t="n"/>
-      <c r="B135" s="8" t="n"/>
+      <c r="B135" s="7" t="n"/>
       <c r="C135" s="8" t="n"/>
       <c r="D135" s="7" t="n"/>
       <c r="E135" s="7" t="n"/>
@@ -3328,12 +3186,11 @@
       <c r="K135" s="8" t="n"/>
       <c r="L135" s="7" t="n"/>
       <c r="M135" s="7" t="n"/>
-      <c r="N135" s="7" t="n"/>
-      <c r="O135" s="8" t="n"/>
+      <c r="N135" s="8" t="n"/>
     </row>
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="7" t="n"/>
-      <c r="B136" s="8" t="n"/>
+      <c r="B136" s="7" t="n"/>
       <c r="C136" s="8" t="n"/>
       <c r="D136" s="7" t="n"/>
       <c r="E136" s="7" t="n"/>
@@ -3345,12 +3202,11 @@
       <c r="K136" s="8" t="n"/>
       <c r="L136" s="7" t="n"/>
       <c r="M136" s="7" t="n"/>
-      <c r="N136" s="7" t="n"/>
-      <c r="O136" s="8" t="n"/>
+      <c r="N136" s="8" t="n"/>
     </row>
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="7" t="n"/>
-      <c r="B137" s="8" t="n"/>
+      <c r="B137" s="7" t="n"/>
       <c r="C137" s="8" t="n"/>
       <c r="D137" s="7" t="n"/>
       <c r="E137" s="7" t="n"/>
@@ -3362,12 +3218,11 @@
       <c r="K137" s="8" t="n"/>
       <c r="L137" s="7" t="n"/>
       <c r="M137" s="7" t="n"/>
-      <c r="N137" s="7" t="n"/>
-      <c r="O137" s="8" t="n"/>
+      <c r="N137" s="8" t="n"/>
     </row>
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="7" t="n"/>
-      <c r="B138" s="8" t="n"/>
+      <c r="B138" s="7" t="n"/>
       <c r="C138" s="8" t="n"/>
       <c r="D138" s="7" t="n"/>
       <c r="E138" s="7" t="n"/>
@@ -3379,12 +3234,11 @@
       <c r="K138" s="8" t="n"/>
       <c r="L138" s="7" t="n"/>
       <c r="M138" s="7" t="n"/>
-      <c r="N138" s="7" t="n"/>
-      <c r="O138" s="8" t="n"/>
+      <c r="N138" s="8" t="n"/>
     </row>
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="7" t="n"/>
-      <c r="B139" s="8" t="n"/>
+      <c r="B139" s="7" t="n"/>
       <c r="C139" s="8" t="n"/>
       <c r="D139" s="7" t="n"/>
       <c r="E139" s="7" t="n"/>
@@ -3396,12 +3250,11 @@
       <c r="K139" s="8" t="n"/>
       <c r="L139" s="7" t="n"/>
       <c r="M139" s="7" t="n"/>
-      <c r="N139" s="7" t="n"/>
-      <c r="O139" s="8" t="n"/>
+      <c r="N139" s="8" t="n"/>
     </row>
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="7" t="n"/>
-      <c r="B140" s="8" t="n"/>
+      <c r="B140" s="7" t="n"/>
       <c r="C140" s="8" t="n"/>
       <c r="D140" s="7" t="n"/>
       <c r="E140" s="7" t="n"/>
@@ -3413,12 +3266,11 @@
       <c r="K140" s="8" t="n"/>
       <c r="L140" s="7" t="n"/>
       <c r="M140" s="7" t="n"/>
-      <c r="N140" s="7" t="n"/>
-      <c r="O140" s="8" t="n"/>
+      <c r="N140" s="8" t="n"/>
     </row>
     <row r="141" ht="22" customHeight="1">
       <c r="A141" s="7" t="n"/>
-      <c r="B141" s="8" t="n"/>
+      <c r="B141" s="7" t="n"/>
       <c r="C141" s="8" t="n"/>
       <c r="D141" s="7" t="n"/>
       <c r="E141" s="7" t="n"/>
@@ -3430,12 +3282,11 @@
       <c r="K141" s="8" t="n"/>
       <c r="L141" s="7" t="n"/>
       <c r="M141" s="7" t="n"/>
-      <c r="N141" s="7" t="n"/>
-      <c r="O141" s="8" t="n"/>
+      <c r="N141" s="8" t="n"/>
     </row>
     <row r="142" ht="22" customHeight="1">
       <c r="A142" s="7" t="n"/>
-      <c r="B142" s="8" t="n"/>
+      <c r="B142" s="7" t="n"/>
       <c r="C142" s="8" t="n"/>
       <c r="D142" s="7" t="n"/>
       <c r="E142" s="7" t="n"/>
@@ -3447,12 +3298,11 @@
       <c r="K142" s="8" t="n"/>
       <c r="L142" s="7" t="n"/>
       <c r="M142" s="7" t="n"/>
-      <c r="N142" s="7" t="n"/>
-      <c r="O142" s="8" t="n"/>
+      <c r="N142" s="8" t="n"/>
     </row>
     <row r="143" ht="22" customHeight="1">
       <c r="A143" s="7" t="n"/>
-      <c r="B143" s="8" t="n"/>
+      <c r="B143" s="7" t="n"/>
       <c r="C143" s="8" t="n"/>
       <c r="D143" s="7" t="n"/>
       <c r="E143" s="7" t="n"/>
@@ -3464,12 +3314,11 @@
       <c r="K143" s="8" t="n"/>
       <c r="L143" s="7" t="n"/>
       <c r="M143" s="7" t="n"/>
-      <c r="N143" s="7" t="n"/>
-      <c r="O143" s="8" t="n"/>
+      <c r="N143" s="8" t="n"/>
     </row>
     <row r="144" ht="22" customHeight="1">
       <c r="A144" s="7" t="n"/>
-      <c r="B144" s="8" t="n"/>
+      <c r="B144" s="7" t="n"/>
       <c r="C144" s="8" t="n"/>
       <c r="D144" s="7" t="n"/>
       <c r="E144" s="7" t="n"/>
@@ -3481,12 +3330,11 @@
       <c r="K144" s="8" t="n"/>
       <c r="L144" s="7" t="n"/>
       <c r="M144" s="7" t="n"/>
-      <c r="N144" s="7" t="n"/>
-      <c r="O144" s="8" t="n"/>
+      <c r="N144" s="8" t="n"/>
     </row>
     <row r="145" ht="22" customHeight="1">
       <c r="A145" s="7" t="n"/>
-      <c r="B145" s="8" t="n"/>
+      <c r="B145" s="7" t="n"/>
       <c r="C145" s="8" t="n"/>
       <c r="D145" s="7" t="n"/>
       <c r="E145" s="7" t="n"/>
@@ -3498,12 +3346,11 @@
       <c r="K145" s="8" t="n"/>
       <c r="L145" s="7" t="n"/>
       <c r="M145" s="7" t="n"/>
-      <c r="N145" s="7" t="n"/>
-      <c r="O145" s="8" t="n"/>
+      <c r="N145" s="8" t="n"/>
     </row>
     <row r="146" ht="22" customHeight="1">
       <c r="A146" s="7" t="n"/>
-      <c r="B146" s="8" t="n"/>
+      <c r="B146" s="7" t="n"/>
       <c r="C146" s="8" t="n"/>
       <c r="D146" s="7" t="n"/>
       <c r="E146" s="7" t="n"/>
@@ -3515,12 +3362,11 @@
       <c r="K146" s="8" t="n"/>
       <c r="L146" s="7" t="n"/>
       <c r="M146" s="7" t="n"/>
-      <c r="N146" s="7" t="n"/>
-      <c r="O146" s="8" t="n"/>
+      <c r="N146" s="8" t="n"/>
     </row>
     <row r="147" ht="22" customHeight="1">
       <c r="A147" s="7" t="n"/>
-      <c r="B147" s="8" t="n"/>
+      <c r="B147" s="7" t="n"/>
       <c r="C147" s="8" t="n"/>
       <c r="D147" s="7" t="n"/>
       <c r="E147" s="7" t="n"/>
@@ -3532,12 +3378,11 @@
       <c r="K147" s="8" t="n"/>
       <c r="L147" s="7" t="n"/>
       <c r="M147" s="7" t="n"/>
-      <c r="N147" s="7" t="n"/>
-      <c r="O147" s="8" t="n"/>
+      <c r="N147" s="8" t="n"/>
     </row>
     <row r="148" ht="22" customHeight="1">
       <c r="A148" s="7" t="n"/>
-      <c r="B148" s="8" t="n"/>
+      <c r="B148" s="7" t="n"/>
       <c r="C148" s="8" t="n"/>
       <c r="D148" s="7" t="n"/>
       <c r="E148" s="7" t="n"/>
@@ -3549,12 +3394,11 @@
       <c r="K148" s="8" t="n"/>
       <c r="L148" s="7" t="n"/>
       <c r="M148" s="7" t="n"/>
-      <c r="N148" s="7" t="n"/>
-      <c r="O148" s="8" t="n"/>
+      <c r="N148" s="8" t="n"/>
     </row>
     <row r="149" ht="22" customHeight="1">
       <c r="A149" s="7" t="n"/>
-      <c r="B149" s="8" t="n"/>
+      <c r="B149" s="7" t="n"/>
       <c r="C149" s="8" t="n"/>
       <c r="D149" s="7" t="n"/>
       <c r="E149" s="7" t="n"/>
@@ -3566,12 +3410,11 @@
       <c r="K149" s="8" t="n"/>
       <c r="L149" s="7" t="n"/>
       <c r="M149" s="7" t="n"/>
-      <c r="N149" s="7" t="n"/>
-      <c r="O149" s="8" t="n"/>
+      <c r="N149" s="8" t="n"/>
     </row>
     <row r="150" ht="22" customHeight="1">
       <c r="A150" s="7" t="n"/>
-      <c r="B150" s="8" t="n"/>
+      <c r="B150" s="7" t="n"/>
       <c r="C150" s="8" t="n"/>
       <c r="D150" s="7" t="n"/>
       <c r="E150" s="7" t="n"/>
@@ -3583,12 +3426,11 @@
       <c r="K150" s="8" t="n"/>
       <c r="L150" s="7" t="n"/>
       <c r="M150" s="7" t="n"/>
-      <c r="N150" s="7" t="n"/>
-      <c r="O150" s="8" t="n"/>
+      <c r="N150" s="8" t="n"/>
     </row>
     <row r="151" ht="22" customHeight="1">
       <c r="A151" s="7" t="n"/>
-      <c r="B151" s="8" t="n"/>
+      <c r="B151" s="7" t="n"/>
       <c r="C151" s="8" t="n"/>
       <c r="D151" s="7" t="n"/>
       <c r="E151" s="7" t="n"/>
@@ -3600,12 +3442,11 @@
       <c r="K151" s="8" t="n"/>
       <c r="L151" s="7" t="n"/>
       <c r="M151" s="7" t="n"/>
-      <c r="N151" s="7" t="n"/>
-      <c r="O151" s="8" t="n"/>
+      <c r="N151" s="8" t="n"/>
     </row>
     <row r="152" ht="22" customHeight="1">
       <c r="A152" s="7" t="n"/>
-      <c r="B152" s="8" t="n"/>
+      <c r="B152" s="7" t="n"/>
       <c r="C152" s="8" t="n"/>
       <c r="D152" s="7" t="n"/>
       <c r="E152" s="7" t="n"/>
@@ -3617,12 +3458,11 @@
       <c r="K152" s="8" t="n"/>
       <c r="L152" s="7" t="n"/>
       <c r="M152" s="7" t="n"/>
-      <c r="N152" s="7" t="n"/>
-      <c r="O152" s="8" t="n"/>
+      <c r="N152" s="8" t="n"/>
     </row>
     <row r="153" ht="22" customHeight="1">
       <c r="A153" s="7" t="n"/>
-      <c r="B153" s="8" t="n"/>
+      <c r="B153" s="7" t="n"/>
       <c r="C153" s="8" t="n"/>
       <c r="D153" s="7" t="n"/>
       <c r="E153" s="7" t="n"/>
@@ -3634,12 +3474,11 @@
       <c r="K153" s="8" t="n"/>
       <c r="L153" s="7" t="n"/>
       <c r="M153" s="7" t="n"/>
-      <c r="N153" s="7" t="n"/>
-      <c r="O153" s="8" t="n"/>
+      <c r="N153" s="8" t="n"/>
     </row>
     <row r="154" ht="22" customHeight="1">
       <c r="A154" s="7" t="n"/>
-      <c r="B154" s="8" t="n"/>
+      <c r="B154" s="7" t="n"/>
       <c r="C154" s="8" t="n"/>
       <c r="D154" s="7" t="n"/>
       <c r="E154" s="7" t="n"/>
@@ -3651,12 +3490,11 @@
       <c r="K154" s="8" t="n"/>
       <c r="L154" s="7" t="n"/>
       <c r="M154" s="7" t="n"/>
-      <c r="N154" s="7" t="n"/>
-      <c r="O154" s="8" t="n"/>
+      <c r="N154" s="8" t="n"/>
     </row>
     <row r="155" ht="22" customHeight="1">
       <c r="A155" s="7" t="n"/>
-      <c r="B155" s="8" t="n"/>
+      <c r="B155" s="7" t="n"/>
       <c r="C155" s="8" t="n"/>
       <c r="D155" s="7" t="n"/>
       <c r="E155" s="7" t="n"/>
@@ -3668,12 +3506,11 @@
       <c r="K155" s="8" t="n"/>
       <c r="L155" s="7" t="n"/>
       <c r="M155" s="7" t="n"/>
-      <c r="N155" s="7" t="n"/>
-      <c r="O155" s="8" t="n"/>
+      <c r="N155" s="8" t="n"/>
     </row>
     <row r="156" ht="22" customHeight="1">
       <c r="A156" s="7" t="n"/>
-      <c r="B156" s="8" t="n"/>
+      <c r="B156" s="7" t="n"/>
       <c r="C156" s="8" t="n"/>
       <c r="D156" s="7" t="n"/>
       <c r="E156" s="7" t="n"/>
@@ -3685,12 +3522,11 @@
       <c r="K156" s="8" t="n"/>
       <c r="L156" s="7" t="n"/>
       <c r="M156" s="7" t="n"/>
-      <c r="N156" s="7" t="n"/>
-      <c r="O156" s="8" t="n"/>
+      <c r="N156" s="8" t="n"/>
     </row>
     <row r="157" ht="22" customHeight="1">
       <c r="A157" s="7" t="n"/>
-      <c r="B157" s="8" t="n"/>
+      <c r="B157" s="7" t="n"/>
       <c r="C157" s="8" t="n"/>
       <c r="D157" s="7" t="n"/>
       <c r="E157" s="7" t="n"/>
@@ -3702,12 +3538,11 @@
       <c r="K157" s="8" t="n"/>
       <c r="L157" s="7" t="n"/>
       <c r="M157" s="7" t="n"/>
-      <c r="N157" s="7" t="n"/>
-      <c r="O157" s="8" t="n"/>
+      <c r="N157" s="8" t="n"/>
     </row>
     <row r="158" ht="22" customHeight="1">
       <c r="A158" s="7" t="n"/>
-      <c r="B158" s="8" t="n"/>
+      <c r="B158" s="7" t="n"/>
       <c r="C158" s="8" t="n"/>
       <c r="D158" s="7" t="n"/>
       <c r="E158" s="7" t="n"/>
@@ -3719,12 +3554,11 @@
       <c r="K158" s="8" t="n"/>
       <c r="L158" s="7" t="n"/>
       <c r="M158" s="7" t="n"/>
-      <c r="N158" s="7" t="n"/>
-      <c r="O158" s="8" t="n"/>
+      <c r="N158" s="8" t="n"/>
     </row>
     <row r="159" ht="22" customHeight="1">
       <c r="A159" s="7" t="n"/>
-      <c r="B159" s="8" t="n"/>
+      <c r="B159" s="7" t="n"/>
       <c r="C159" s="8" t="n"/>
       <c r="D159" s="7" t="n"/>
       <c r="E159" s="7" t="n"/>
@@ -3736,12 +3570,11 @@
       <c r="K159" s="8" t="n"/>
       <c r="L159" s="7" t="n"/>
       <c r="M159" s="7" t="n"/>
-      <c r="N159" s="7" t="n"/>
-      <c r="O159" s="8" t="n"/>
+      <c r="N159" s="8" t="n"/>
     </row>
     <row r="160" ht="22" customHeight="1">
       <c r="A160" s="7" t="n"/>
-      <c r="B160" s="8" t="n"/>
+      <c r="B160" s="7" t="n"/>
       <c r="C160" s="8" t="n"/>
       <c r="D160" s="7" t="n"/>
       <c r="E160" s="7" t="n"/>
@@ -3753,12 +3586,11 @@
       <c r="K160" s="8" t="n"/>
       <c r="L160" s="7" t="n"/>
       <c r="M160" s="7" t="n"/>
-      <c r="N160" s="7" t="n"/>
-      <c r="O160" s="8" t="n"/>
+      <c r="N160" s="8" t="n"/>
     </row>
     <row r="161" ht="22" customHeight="1">
       <c r="A161" s="7" t="n"/>
-      <c r="B161" s="8" t="n"/>
+      <c r="B161" s="7" t="n"/>
       <c r="C161" s="8" t="n"/>
       <c r="D161" s="7" t="n"/>
       <c r="E161" s="7" t="n"/>
@@ -3770,12 +3602,11 @@
       <c r="K161" s="8" t="n"/>
       <c r="L161" s="7" t="n"/>
       <c r="M161" s="7" t="n"/>
-      <c r="N161" s="7" t="n"/>
-      <c r="O161" s="8" t="n"/>
+      <c r="N161" s="8" t="n"/>
     </row>
     <row r="162" ht="22" customHeight="1">
       <c r="A162" s="7" t="n"/>
-      <c r="B162" s="8" t="n"/>
+      <c r="B162" s="7" t="n"/>
       <c r="C162" s="8" t="n"/>
       <c r="D162" s="7" t="n"/>
       <c r="E162" s="7" t="n"/>
@@ -3787,12 +3618,11 @@
       <c r="K162" s="8" t="n"/>
       <c r="L162" s="7" t="n"/>
       <c r="M162" s="7" t="n"/>
-      <c r="N162" s="7" t="n"/>
-      <c r="O162" s="8" t="n"/>
+      <c r="N162" s="8" t="n"/>
     </row>
     <row r="163" ht="22" customHeight="1">
       <c r="A163" s="7" t="n"/>
-      <c r="B163" s="8" t="n"/>
+      <c r="B163" s="7" t="n"/>
       <c r="C163" s="8" t="n"/>
       <c r="D163" s="7" t="n"/>
       <c r="E163" s="7" t="n"/>
@@ -3804,12 +3634,11 @@
       <c r="K163" s="8" t="n"/>
       <c r="L163" s="7" t="n"/>
       <c r="M163" s="7" t="n"/>
-      <c r="N163" s="7" t="n"/>
-      <c r="O163" s="8" t="n"/>
+      <c r="N163" s="8" t="n"/>
     </row>
     <row r="164" ht="22" customHeight="1">
       <c r="A164" s="7" t="n"/>
-      <c r="B164" s="8" t="n"/>
+      <c r="B164" s="7" t="n"/>
       <c r="C164" s="8" t="n"/>
       <c r="D164" s="7" t="n"/>
       <c r="E164" s="7" t="n"/>
@@ -3821,12 +3650,11 @@
       <c r="K164" s="8" t="n"/>
       <c r="L164" s="7" t="n"/>
       <c r="M164" s="7" t="n"/>
-      <c r="N164" s="7" t="n"/>
-      <c r="O164" s="8" t="n"/>
+      <c r="N164" s="8" t="n"/>
     </row>
     <row r="165" ht="22" customHeight="1">
       <c r="A165" s="7" t="n"/>
-      <c r="B165" s="8" t="n"/>
+      <c r="B165" s="7" t="n"/>
       <c r="C165" s="8" t="n"/>
       <c r="D165" s="7" t="n"/>
       <c r="E165" s="7" t="n"/>
@@ -3838,12 +3666,11 @@
       <c r="K165" s="8" t="n"/>
       <c r="L165" s="7" t="n"/>
       <c r="M165" s="7" t="n"/>
-      <c r="N165" s="7" t="n"/>
-      <c r="O165" s="8" t="n"/>
+      <c r="N165" s="8" t="n"/>
     </row>
     <row r="166" ht="22" customHeight="1">
       <c r="A166" s="7" t="n"/>
-      <c r="B166" s="8" t="n"/>
+      <c r="B166" s="7" t="n"/>
       <c r="C166" s="8" t="n"/>
       <c r="D166" s="7" t="n"/>
       <c r="E166" s="7" t="n"/>
@@ -3855,12 +3682,11 @@
       <c r="K166" s="8" t="n"/>
       <c r="L166" s="7" t="n"/>
       <c r="M166" s="7" t="n"/>
-      <c r="N166" s="7" t="n"/>
-      <c r="O166" s="8" t="n"/>
+      <c r="N166" s="8" t="n"/>
     </row>
     <row r="167" ht="22" customHeight="1">
       <c r="A167" s="7" t="n"/>
-      <c r="B167" s="8" t="n"/>
+      <c r="B167" s="7" t="n"/>
       <c r="C167" s="8" t="n"/>
       <c r="D167" s="7" t="n"/>
       <c r="E167" s="7" t="n"/>
@@ -3872,12 +3698,11 @@
       <c r="K167" s="8" t="n"/>
       <c r="L167" s="7" t="n"/>
       <c r="M167" s="7" t="n"/>
-      <c r="N167" s="7" t="n"/>
-      <c r="O167" s="8" t="n"/>
+      <c r="N167" s="8" t="n"/>
     </row>
     <row r="168" ht="22" customHeight="1">
       <c r="A168" s="7" t="n"/>
-      <c r="B168" s="8" t="n"/>
+      <c r="B168" s="7" t="n"/>
       <c r="C168" s="8" t="n"/>
       <c r="D168" s="7" t="n"/>
       <c r="E168" s="7" t="n"/>
@@ -3889,12 +3714,11 @@
       <c r="K168" s="8" t="n"/>
       <c r="L168" s="7" t="n"/>
       <c r="M168" s="7" t="n"/>
-      <c r="N168" s="7" t="n"/>
-      <c r="O168" s="8" t="n"/>
+      <c r="N168" s="8" t="n"/>
     </row>
     <row r="169" ht="22" customHeight="1">
       <c r="A169" s="7" t="n"/>
-      <c r="B169" s="8" t="n"/>
+      <c r="B169" s="7" t="n"/>
       <c r="C169" s="8" t="n"/>
       <c r="D169" s="7" t="n"/>
       <c r="E169" s="7" t="n"/>
@@ -3906,12 +3730,11 @@
       <c r="K169" s="8" t="n"/>
       <c r="L169" s="7" t="n"/>
       <c r="M169" s="7" t="n"/>
-      <c r="N169" s="7" t="n"/>
-      <c r="O169" s="8" t="n"/>
+      <c r="N169" s="8" t="n"/>
     </row>
     <row r="170" ht="22" customHeight="1">
       <c r="A170" s="7" t="n"/>
-      <c r="B170" s="8" t="n"/>
+      <c r="B170" s="7" t="n"/>
       <c r="C170" s="8" t="n"/>
       <c r="D170" s="7" t="n"/>
       <c r="E170" s="7" t="n"/>
@@ -3923,12 +3746,11 @@
       <c r="K170" s="8" t="n"/>
       <c r="L170" s="7" t="n"/>
       <c r="M170" s="7" t="n"/>
-      <c r="N170" s="7" t="n"/>
-      <c r="O170" s="8" t="n"/>
+      <c r="N170" s="8" t="n"/>
     </row>
     <row r="171" ht="22" customHeight="1">
       <c r="A171" s="7" t="n"/>
-      <c r="B171" s="8" t="n"/>
+      <c r="B171" s="7" t="n"/>
       <c r="C171" s="8" t="n"/>
       <c r="D171" s="7" t="n"/>
       <c r="E171" s="7" t="n"/>
@@ -3940,12 +3762,11 @@
       <c r="K171" s="8" t="n"/>
       <c r="L171" s="7" t="n"/>
       <c r="M171" s="7" t="n"/>
-      <c r="N171" s="7" t="n"/>
-      <c r="O171" s="8" t="n"/>
+      <c r="N171" s="8" t="n"/>
     </row>
     <row r="172" ht="22" customHeight="1">
       <c r="A172" s="7" t="n"/>
-      <c r="B172" s="8" t="n"/>
+      <c r="B172" s="7" t="n"/>
       <c r="C172" s="8" t="n"/>
       <c r="D172" s="7" t="n"/>
       <c r="E172" s="7" t="n"/>
@@ -3957,12 +3778,11 @@
       <c r="K172" s="8" t="n"/>
       <c r="L172" s="7" t="n"/>
       <c r="M172" s="7" t="n"/>
-      <c r="N172" s="7" t="n"/>
-      <c r="O172" s="8" t="n"/>
+      <c r="N172" s="8" t="n"/>
     </row>
     <row r="173" ht="22" customHeight="1">
       <c r="A173" s="7" t="n"/>
-      <c r="B173" s="8" t="n"/>
+      <c r="B173" s="7" t="n"/>
       <c r="C173" s="8" t="n"/>
       <c r="D173" s="7" t="n"/>
       <c r="E173" s="7" t="n"/>
@@ -3974,12 +3794,11 @@
       <c r="K173" s="8" t="n"/>
       <c r="L173" s="7" t="n"/>
       <c r="M173" s="7" t="n"/>
-      <c r="N173" s="7" t="n"/>
-      <c r="O173" s="8" t="n"/>
+      <c r="N173" s="8" t="n"/>
     </row>
     <row r="174" ht="22" customHeight="1">
       <c r="A174" s="7" t="n"/>
-      <c r="B174" s="8" t="n"/>
+      <c r="B174" s="7" t="n"/>
       <c r="C174" s="8" t="n"/>
       <c r="D174" s="7" t="n"/>
       <c r="E174" s="7" t="n"/>
@@ -3991,12 +3810,11 @@
       <c r="K174" s="8" t="n"/>
       <c r="L174" s="7" t="n"/>
       <c r="M174" s="7" t="n"/>
-      <c r="N174" s="7" t="n"/>
-      <c r="O174" s="8" t="n"/>
+      <c r="N174" s="8" t="n"/>
     </row>
     <row r="175" ht="22" customHeight="1">
       <c r="A175" s="7" t="n"/>
-      <c r="B175" s="8" t="n"/>
+      <c r="B175" s="7" t="n"/>
       <c r="C175" s="8" t="n"/>
       <c r="D175" s="7" t="n"/>
       <c r="E175" s="7" t="n"/>
@@ -4008,12 +3826,11 @@
       <c r="K175" s="8" t="n"/>
       <c r="L175" s="7" t="n"/>
       <c r="M175" s="7" t="n"/>
-      <c r="N175" s="7" t="n"/>
-      <c r="O175" s="8" t="n"/>
+      <c r="N175" s="8" t="n"/>
     </row>
     <row r="176" ht="22" customHeight="1">
       <c r="A176" s="7" t="n"/>
-      <c r="B176" s="8" t="n"/>
+      <c r="B176" s="7" t="n"/>
       <c r="C176" s="8" t="n"/>
       <c r="D176" s="7" t="n"/>
       <c r="E176" s="7" t="n"/>
@@ -4025,12 +3842,11 @@
       <c r="K176" s="8" t="n"/>
       <c r="L176" s="7" t="n"/>
       <c r="M176" s="7" t="n"/>
-      <c r="N176" s="7" t="n"/>
-      <c r="O176" s="8" t="n"/>
+      <c r="N176" s="8" t="n"/>
     </row>
     <row r="177" ht="22" customHeight="1">
       <c r="A177" s="7" t="n"/>
-      <c r="B177" s="8" t="n"/>
+      <c r="B177" s="7" t="n"/>
       <c r="C177" s="8" t="n"/>
       <c r="D177" s="7" t="n"/>
       <c r="E177" s="7" t="n"/>
@@ -4042,12 +3858,11 @@
       <c r="K177" s="8" t="n"/>
       <c r="L177" s="7" t="n"/>
       <c r="M177" s="7" t="n"/>
-      <c r="N177" s="7" t="n"/>
-      <c r="O177" s="8" t="n"/>
+      <c r="N177" s="8" t="n"/>
     </row>
     <row r="178" ht="22" customHeight="1">
       <c r="A178" s="7" t="n"/>
-      <c r="B178" s="8" t="n"/>
+      <c r="B178" s="7" t="n"/>
       <c r="C178" s="8" t="n"/>
       <c r="D178" s="7" t="n"/>
       <c r="E178" s="7" t="n"/>
@@ -4059,12 +3874,11 @@
       <c r="K178" s="8" t="n"/>
       <c r="L178" s="7" t="n"/>
       <c r="M178" s="7" t="n"/>
-      <c r="N178" s="7" t="n"/>
-      <c r="O178" s="8" t="n"/>
+      <c r="N178" s="8" t="n"/>
     </row>
     <row r="179" ht="22" customHeight="1">
       <c r="A179" s="7" t="n"/>
-      <c r="B179" s="8" t="n"/>
+      <c r="B179" s="7" t="n"/>
       <c r="C179" s="8" t="n"/>
       <c r="D179" s="7" t="n"/>
       <c r="E179" s="7" t="n"/>
@@ -4076,12 +3890,11 @@
       <c r="K179" s="8" t="n"/>
       <c r="L179" s="7" t="n"/>
       <c r="M179" s="7" t="n"/>
-      <c r="N179" s="7" t="n"/>
-      <c r="O179" s="8" t="n"/>
+      <c r="N179" s="8" t="n"/>
     </row>
     <row r="180" ht="22" customHeight="1">
       <c r="A180" s="7" t="n"/>
-      <c r="B180" s="8" t="n"/>
+      <c r="B180" s="7" t="n"/>
       <c r="C180" s="8" t="n"/>
       <c r="D180" s="7" t="n"/>
       <c r="E180" s="7" t="n"/>
@@ -4093,12 +3906,11 @@
       <c r="K180" s="8" t="n"/>
       <c r="L180" s="7" t="n"/>
       <c r="M180" s="7" t="n"/>
-      <c r="N180" s="7" t="n"/>
-      <c r="O180" s="8" t="n"/>
+      <c r="N180" s="8" t="n"/>
     </row>
     <row r="181" ht="22" customHeight="1">
       <c r="A181" s="7" t="n"/>
-      <c r="B181" s="8" t="n"/>
+      <c r="B181" s="7" t="n"/>
       <c r="C181" s="8" t="n"/>
       <c r="D181" s="7" t="n"/>
       <c r="E181" s="7" t="n"/>
@@ -4110,12 +3922,11 @@
       <c r="K181" s="8" t="n"/>
       <c r="L181" s="7" t="n"/>
       <c r="M181" s="7" t="n"/>
-      <c r="N181" s="7" t="n"/>
-      <c r="O181" s="8" t="n"/>
+      <c r="N181" s="8" t="n"/>
     </row>
     <row r="182" ht="22" customHeight="1">
       <c r="A182" s="7" t="n"/>
-      <c r="B182" s="8" t="n"/>
+      <c r="B182" s="7" t="n"/>
       <c r="C182" s="8" t="n"/>
       <c r="D182" s="7" t="n"/>
       <c r="E182" s="7" t="n"/>
@@ -4127,12 +3938,11 @@
       <c r="K182" s="8" t="n"/>
       <c r="L182" s="7" t="n"/>
       <c r="M182" s="7" t="n"/>
-      <c r="N182" s="7" t="n"/>
-      <c r="O182" s="8" t="n"/>
+      <c r="N182" s="8" t="n"/>
     </row>
     <row r="183" ht="22" customHeight="1">
       <c r="A183" s="7" t="n"/>
-      <c r="B183" s="8" t="n"/>
+      <c r="B183" s="7" t="n"/>
       <c r="C183" s="8" t="n"/>
       <c r="D183" s="7" t="n"/>
       <c r="E183" s="7" t="n"/>
@@ -4144,12 +3954,11 @@
       <c r="K183" s="8" t="n"/>
       <c r="L183" s="7" t="n"/>
       <c r="M183" s="7" t="n"/>
-      <c r="N183" s="7" t="n"/>
-      <c r="O183" s="8" t="n"/>
+      <c r="N183" s="8" t="n"/>
     </row>
     <row r="184" ht="22" customHeight="1">
       <c r="A184" s="7" t="n"/>
-      <c r="B184" s="8" t="n"/>
+      <c r="B184" s="7" t="n"/>
       <c r="C184" s="8" t="n"/>
       <c r="D184" s="7" t="n"/>
       <c r="E184" s="7" t="n"/>
@@ -4161,12 +3970,11 @@
       <c r="K184" s="8" t="n"/>
       <c r="L184" s="7" t="n"/>
       <c r="M184" s="7" t="n"/>
-      <c r="N184" s="7" t="n"/>
-      <c r="O184" s="8" t="n"/>
+      <c r="N184" s="8" t="n"/>
     </row>
     <row r="185" ht="22" customHeight="1">
       <c r="A185" s="7" t="n"/>
-      <c r="B185" s="8" t="n"/>
+      <c r="B185" s="7" t="n"/>
       <c r="C185" s="8" t="n"/>
       <c r="D185" s="7" t="n"/>
       <c r="E185" s="7" t="n"/>
@@ -4178,12 +3986,11 @@
       <c r="K185" s="8" t="n"/>
       <c r="L185" s="7" t="n"/>
       <c r="M185" s="7" t="n"/>
-      <c r="N185" s="7" t="n"/>
-      <c r="O185" s="8" t="n"/>
+      <c r="N185" s="8" t="n"/>
     </row>
     <row r="186" ht="22" customHeight="1">
       <c r="A186" s="7" t="n"/>
-      <c r="B186" s="8" t="n"/>
+      <c r="B186" s="7" t="n"/>
       <c r="C186" s="8" t="n"/>
       <c r="D186" s="7" t="n"/>
       <c r="E186" s="7" t="n"/>
@@ -4195,12 +4002,11 @@
       <c r="K186" s="8" t="n"/>
       <c r="L186" s="7" t="n"/>
       <c r="M186" s="7" t="n"/>
-      <c r="N186" s="7" t="n"/>
-      <c r="O186" s="8" t="n"/>
+      <c r="N186" s="8" t="n"/>
     </row>
     <row r="187" ht="22" customHeight="1">
       <c r="A187" s="7" t="n"/>
-      <c r="B187" s="8" t="n"/>
+      <c r="B187" s="7" t="n"/>
       <c r="C187" s="8" t="n"/>
       <c r="D187" s="7" t="n"/>
       <c r="E187" s="7" t="n"/>
@@ -4212,12 +4018,11 @@
       <c r="K187" s="8" t="n"/>
       <c r="L187" s="7" t="n"/>
       <c r="M187" s="7" t="n"/>
-      <c r="N187" s="7" t="n"/>
-      <c r="O187" s="8" t="n"/>
+      <c r="N187" s="8" t="n"/>
     </row>
     <row r="188" ht="22" customHeight="1">
       <c r="A188" s="7" t="n"/>
-      <c r="B188" s="8" t="n"/>
+      <c r="B188" s="7" t="n"/>
       <c r="C188" s="8" t="n"/>
       <c r="D188" s="7" t="n"/>
       <c r="E188" s="7" t="n"/>
@@ -4229,12 +4034,11 @@
       <c r="K188" s="8" t="n"/>
       <c r="L188" s="7" t="n"/>
       <c r="M188" s="7" t="n"/>
-      <c r="N188" s="7" t="n"/>
-      <c r="O188" s="8" t="n"/>
+      <c r="N188" s="8" t="n"/>
     </row>
     <row r="189" ht="22" customHeight="1">
       <c r="A189" s="7" t="n"/>
-      <c r="B189" s="8" t="n"/>
+      <c r="B189" s="7" t="n"/>
       <c r="C189" s="8" t="n"/>
       <c r="D189" s="7" t="n"/>
       <c r="E189" s="7" t="n"/>
@@ -4246,12 +4050,11 @@
       <c r="K189" s="8" t="n"/>
       <c r="L189" s="7" t="n"/>
       <c r="M189" s="7" t="n"/>
-      <c r="N189" s="7" t="n"/>
-      <c r="O189" s="8" t="n"/>
+      <c r="N189" s="8" t="n"/>
     </row>
     <row r="190" ht="22" customHeight="1">
       <c r="A190" s="7" t="n"/>
-      <c r="B190" s="8" t="n"/>
+      <c r="B190" s="7" t="n"/>
       <c r="C190" s="8" t="n"/>
       <c r="D190" s="7" t="n"/>
       <c r="E190" s="7" t="n"/>
@@ -4263,12 +4066,11 @@
       <c r="K190" s="8" t="n"/>
       <c r="L190" s="7" t="n"/>
       <c r="M190" s="7" t="n"/>
-      <c r="N190" s="7" t="n"/>
-      <c r="O190" s="8" t="n"/>
+      <c r="N190" s="8" t="n"/>
     </row>
     <row r="191" ht="22" customHeight="1">
       <c r="A191" s="7" t="n"/>
-      <c r="B191" s="8" t="n"/>
+      <c r="B191" s="7" t="n"/>
       <c r="C191" s="8" t="n"/>
       <c r="D191" s="7" t="n"/>
       <c r="E191" s="7" t="n"/>
@@ -4280,12 +4082,11 @@
       <c r="K191" s="8" t="n"/>
       <c r="L191" s="7" t="n"/>
       <c r="M191" s="7" t="n"/>
-      <c r="N191" s="7" t="n"/>
-      <c r="O191" s="8" t="n"/>
+      <c r="N191" s="8" t="n"/>
     </row>
     <row r="192" ht="22" customHeight="1">
       <c r="A192" s="7" t="n"/>
-      <c r="B192" s="8" t="n"/>
+      <c r="B192" s="7" t="n"/>
       <c r="C192" s="8" t="n"/>
       <c r="D192" s="7" t="n"/>
       <c r="E192" s="7" t="n"/>
@@ -4297,12 +4098,11 @@
       <c r="K192" s="8" t="n"/>
       <c r="L192" s="7" t="n"/>
       <c r="M192" s="7" t="n"/>
-      <c r="N192" s="7" t="n"/>
-      <c r="O192" s="8" t="n"/>
+      <c r="N192" s="8" t="n"/>
     </row>
     <row r="193" ht="22" customHeight="1">
       <c r="A193" s="7" t="n"/>
-      <c r="B193" s="8" t="n"/>
+      <c r="B193" s="7" t="n"/>
       <c r="C193" s="8" t="n"/>
       <c r="D193" s="7" t="n"/>
       <c r="E193" s="7" t="n"/>
@@ -4314,12 +4114,11 @@
       <c r="K193" s="8" t="n"/>
       <c r="L193" s="7" t="n"/>
       <c r="M193" s="7" t="n"/>
-      <c r="N193" s="7" t="n"/>
-      <c r="O193" s="8" t="n"/>
+      <c r="N193" s="8" t="n"/>
     </row>
     <row r="194" ht="22" customHeight="1">
       <c r="A194" s="7" t="n"/>
-      <c r="B194" s="8" t="n"/>
+      <c r="B194" s="7" t="n"/>
       <c r="C194" s="8" t="n"/>
       <c r="D194" s="7" t="n"/>
       <c r="E194" s="7" t="n"/>
@@ -4331,12 +4130,11 @@
       <c r="K194" s="8" t="n"/>
       <c r="L194" s="7" t="n"/>
       <c r="M194" s="7" t="n"/>
-      <c r="N194" s="7" t="n"/>
-      <c r="O194" s="8" t="n"/>
+      <c r="N194" s="8" t="n"/>
     </row>
     <row r="195" ht="22" customHeight="1">
       <c r="A195" s="7" t="n"/>
-      <c r="B195" s="8" t="n"/>
+      <c r="B195" s="7" t="n"/>
       <c r="C195" s="8" t="n"/>
       <c r="D195" s="7" t="n"/>
       <c r="E195" s="7" t="n"/>
@@ -4348,12 +4146,11 @@
       <c r="K195" s="8" t="n"/>
       <c r="L195" s="7" t="n"/>
       <c r="M195" s="7" t="n"/>
-      <c r="N195" s="7" t="n"/>
-      <c r="O195" s="8" t="n"/>
+      <c r="N195" s="8" t="n"/>
     </row>
     <row r="196" ht="22" customHeight="1">
       <c r="A196" s="7" t="n"/>
-      <c r="B196" s="8" t="n"/>
+      <c r="B196" s="7" t="n"/>
       <c r="C196" s="8" t="n"/>
       <c r="D196" s="7" t="n"/>
       <c r="E196" s="7" t="n"/>
@@ -4365,12 +4162,11 @@
       <c r="K196" s="8" t="n"/>
       <c r="L196" s="7" t="n"/>
       <c r="M196" s="7" t="n"/>
-      <c r="N196" s="7" t="n"/>
-      <c r="O196" s="8" t="n"/>
+      <c r="N196" s="8" t="n"/>
     </row>
     <row r="197" ht="22" customHeight="1">
       <c r="A197" s="7" t="n"/>
-      <c r="B197" s="8" t="n"/>
+      <c r="B197" s="7" t="n"/>
       <c r="C197" s="8" t="n"/>
       <c r="D197" s="7" t="n"/>
       <c r="E197" s="7" t="n"/>
@@ -4382,12 +4178,11 @@
       <c r="K197" s="8" t="n"/>
       <c r="L197" s="7" t="n"/>
       <c r="M197" s="7" t="n"/>
-      <c r="N197" s="7" t="n"/>
-      <c r="O197" s="8" t="n"/>
+      <c r="N197" s="8" t="n"/>
     </row>
     <row r="198" ht="22" customHeight="1">
       <c r="A198" s="7" t="n"/>
-      <c r="B198" s="8" t="n"/>
+      <c r="B198" s="7" t="n"/>
       <c r="C198" s="8" t="n"/>
       <c r="D198" s="7" t="n"/>
       <c r="E198" s="7" t="n"/>
@@ -4399,12 +4194,11 @@
       <c r="K198" s="8" t="n"/>
       <c r="L198" s="7" t="n"/>
       <c r="M198" s="7" t="n"/>
-      <c r="N198" s="7" t="n"/>
-      <c r="O198" s="8" t="n"/>
+      <c r="N198" s="8" t="n"/>
     </row>
     <row r="199" ht="22" customHeight="1">
       <c r="A199" s="7" t="n"/>
-      <c r="B199" s="8" t="n"/>
+      <c r="B199" s="7" t="n"/>
       <c r="C199" s="8" t="n"/>
       <c r="D199" s="7" t="n"/>
       <c r="E199" s="7" t="n"/>
@@ -4416,12 +4210,11 @@
       <c r="K199" s="8" t="n"/>
       <c r="L199" s="7" t="n"/>
       <c r="M199" s="7" t="n"/>
-      <c r="N199" s="7" t="n"/>
-      <c r="O199" s="8" t="n"/>
+      <c r="N199" s="8" t="n"/>
     </row>
     <row r="200" ht="22" customHeight="1">
       <c r="A200" s="7" t="n"/>
-      <c r="B200" s="8" t="n"/>
+      <c r="B200" s="7" t="n"/>
       <c r="C200" s="8" t="n"/>
       <c r="D200" s="7" t="n"/>
       <c r="E200" s="7" t="n"/>
@@ -4433,12 +4226,11 @@
       <c r="K200" s="8" t="n"/>
       <c r="L200" s="7" t="n"/>
       <c r="M200" s="7" t="n"/>
-      <c r="N200" s="7" t="n"/>
-      <c r="O200" s="8" t="n"/>
+      <c r="N200" s="8" t="n"/>
     </row>
     <row r="201" ht="22" customHeight="1">
       <c r="A201" s="7" t="n"/>
-      <c r="B201" s="8" t="n"/>
+      <c r="B201" s="7" t="n"/>
       <c r="C201" s="8" t="n"/>
       <c r="D201" s="7" t="n"/>
       <c r="E201" s="7" t="n"/>
@@ -4450,12 +4242,11 @@
       <c r="K201" s="8" t="n"/>
       <c r="L201" s="7" t="n"/>
       <c r="M201" s="7" t="n"/>
-      <c r="N201" s="7" t="n"/>
-      <c r="O201" s="8" t="n"/>
+      <c r="N201" s="8" t="n"/>
     </row>
     <row r="202" ht="22" customHeight="1">
       <c r="A202" s="7" t="n"/>
-      <c r="B202" s="8" t="n"/>
+      <c r="B202" s="7" t="n"/>
       <c r="C202" s="8" t="n"/>
       <c r="D202" s="7" t="n"/>
       <c r="E202" s="7" t="n"/>
@@ -4467,31 +4258,30 @@
       <c r="K202" s="8" t="n"/>
       <c r="L202" s="7" t="n"/>
       <c r="M202" s="7" t="n"/>
-      <c r="N202" s="7" t="n"/>
-      <c r="O202" s="8" t="n"/>
+      <c r="N202" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation sqref="B3:B202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="请从下拉列表中选择" type="list">
       <formula1>"新需求,量产,定制,改造"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"国内,海外"</formula1>
+    <dataValidation sqref="E3:E202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="请从下拉列表中选择市场区域" type="list">
+      <formula1>"拉美区,西欧区,东欧区,中东区,亚太区,土耳其区,非洲区,北美区,OEM业务部"</formula1>
     </dataValidation>
-    <dataValidation sqref="J3:J202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="请从下拉列表中选择阶段类型" type="list">
-      <formula1>"P1 需求评估,P2 配置评估,P3 模块选型,P4 工业设计,P5 结构设计,P6 样机打样,P7 联调测试,P8 交付"</formula1>
+    <dataValidation sqref="F3:F202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="请从下拉列表中选择阶段类型" type="list">
+      <formula1>"需求评估,配置评估,模块选型,工业设计,结构设计,样机打样,联调测试,交付"</formula1>
     </dataValidation>
-    <dataValidation sqref="M3:M202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L3:L202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="请从下拉列表中选择阶段状态" type="list">
       <formula1>"未开始,进行中,已完成,延期,已搁置"</formula1>
     </dataValidation>
-    <dataValidation sqref="N3:N202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="进度请填 0-100" type="whole" operator="between">
+    <dataValidation sqref="M3:M202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="进度请填 0-100" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation sqref="F3:I202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="请填入有效日期" type="date" operator="greaterThan">
+    <dataValidation sqref="G3:J202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="请填入有效日期" type="date" operator="greaterThan">
       <formula1>2024-01-01</formula1>
     </dataValidation>
   </dataValidations>
